--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="224">
   <si>
     <t>targa</t>
   </si>
@@ -395,301 +395,298 @@
     <t>MICAELA.POSTIGLIONE</t>
   </si>
   <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>PASQUARELLI - IN ASSISTENA</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>MAGRI MARILENA</t>
   </si>
   <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
     <t>CIMINO NORA (LA SUA FERMA DA PASQUARELLI )</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>RUSSO.ZAIRA</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1044,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1058,7 +1055,7 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1096,7 +1093,7 @@
         <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1123,7 +1120,7 @@
         <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1150,7 +1147,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1161,7 +1158,7 @@
         <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1188,7 +1185,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1199,7 +1196,7 @@
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1210,7 +1207,7 @@
         <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1221,7 +1218,7 @@
         <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1232,7 +1229,7 @@
         <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1299,7 +1296,7 @@
         <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1310,7 +1307,7 @@
         <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1337,7 +1334,7 @@
         <v>130</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1412,7 +1409,7 @@
         <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1460,7 +1457,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1468,7 +1465,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1476,10 +1473,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1487,10 +1484,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1498,7 +1495,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1506,7 +1503,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1514,7 +1511,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1522,10 +1519,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1533,7 +1530,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1541,7 +1538,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1549,7 +1546,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1557,7 +1554,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1565,10 +1562,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1576,7 +1573,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1584,7 +1581,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1592,7 +1589,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1600,7 +1597,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1608,10 +1605,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C65" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1619,7 +1616,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1627,7 +1624,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1635,7 +1632,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1643,7 +1640,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1651,7 +1648,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1659,7 +1656,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1667,10 +1664,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1678,10 +1675,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1689,10 +1686,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C74" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1700,10 +1697,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1711,10 +1708,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1722,7 +1719,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1730,7 +1727,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1738,10 +1735,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1749,7 +1746,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1757,7 +1754,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1765,10 +1762,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1776,10 +1773,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C83" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1787,7 +1784,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1795,7 +1792,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1803,7 +1800,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1811,7 +1808,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1819,10 +1816,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C88" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1830,7 +1827,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1841,7 +1838,7 @@
         <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1849,7 +1846,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1857,7 +1854,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1865,7 +1862,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1873,7 +1870,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1881,10 +1878,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C95" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1892,10 +1889,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1903,10 +1900,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C97" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1914,10 +1911,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -1927,35 +1924,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" t="s">
         <v>220</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>221</v>
-      </c>
-      <c r="C1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="223">
   <si>
     <t>targa</t>
   </si>
@@ -407,286 +407,283 @@
     <t>FEDERICA.DIREMIGIO</t>
   </si>
   <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
     <t>PASQUARELLI - IN ASSISTENA</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
-  </si>
-  <si>
-    <t>CIMINO NORA (LA SUA FERMA DA PASQUARELLI )</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1041,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1055,7 +1052,7 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1093,7 +1090,7 @@
         <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1120,7 +1117,7 @@
         <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1147,7 +1144,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1158,7 +1155,7 @@
         <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1185,7 +1182,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1196,7 +1193,7 @@
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1207,7 +1204,7 @@
         <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1218,7 +1215,7 @@
         <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1229,7 +1226,7 @@
         <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1296,7 +1293,7 @@
         <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1307,7 +1304,7 @@
         <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1331,7 +1328,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
         <v>200</v>
@@ -1342,7 +1339,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1350,7 +1347,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1358,7 +1355,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1366,7 +1363,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1374,7 +1371,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1382,7 +1379,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1390,7 +1387,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>126</v>
+      </c>
+      <c r="C40" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1398,7 +1398,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1406,10 +1406,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1417,7 +1417,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1425,7 +1425,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1433,7 +1433,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1441,7 +1441,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1449,7 +1449,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1465,7 +1465,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1473,10 +1473,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1484,10 +1484,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1495,7 +1495,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1503,7 +1503,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1511,7 +1511,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1519,10 +1519,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1530,7 +1530,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1538,7 +1538,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1546,7 +1546,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1554,7 +1554,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1562,10 +1562,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1573,7 +1573,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1581,7 +1581,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1589,7 +1589,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1597,7 +1597,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1605,10 +1605,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1616,7 +1616,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1624,7 +1624,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1632,7 +1632,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1640,7 +1640,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1648,7 +1648,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1656,7 +1656,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1664,10 +1664,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1678,7 +1678,7 @@
         <v>126</v>
       </c>
       <c r="C73" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1689,7 +1689,7 @@
         <v>126</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1697,10 +1697,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1708,10 +1708,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1719,7 +1719,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1727,7 +1727,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1735,10 +1735,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C79" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1746,7 +1746,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1754,7 +1754,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1762,10 +1762,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C82" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1773,10 +1773,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C83" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1784,7 +1784,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1792,7 +1792,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1800,7 +1800,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1808,7 +1808,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1816,10 +1816,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C88" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1827,7 +1827,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1838,7 +1838,7 @@
         <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1846,7 +1846,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1854,7 +1854,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1862,7 +1862,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1870,7 +1870,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1881,7 +1881,7 @@
         <v>126</v>
       </c>
       <c r="C95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1892,7 +1892,7 @@
         <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1903,7 +1903,7 @@
         <v>126</v>
       </c>
       <c r="C97" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1911,10 +1911,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C98" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -1929,24 +1929,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" t="s">
         <v>218</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>219</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>220</v>
-      </c>
-      <c r="D1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
         <v>126</v>
@@ -1960,10 +1960,10 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
         <v>200</v>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="222">
   <si>
     <t>targa</t>
   </si>
@@ -320,6 +320,9 @@
     <t>DA ASSEGNARE</t>
   </si>
   <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
     <t>STEFANO.CAMPLONE</t>
   </si>
   <si>
@@ -482,208 +485,202 @@
     <t>NARDECCHIA CHIARA</t>
   </si>
   <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>PASQUARELLI - IN ASSISTENA</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1046,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
         <v>188</v>
@@ -1060,7 +1057,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1068,7 +1065,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1076,7 +1073,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="1">
         <v>45851</v>
@@ -1087,7 +1084,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
         <v>189</v>
@@ -1098,7 +1095,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1106,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1114,7 +1111,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
         <v>190</v>
@@ -1125,7 +1122,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1133,7 +1130,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1141,7 +1138,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
         <v>191</v>
@@ -1152,7 +1149,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
         <v>192</v>
@@ -1163,7 +1160,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1171,7 +1168,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1179,7 +1176,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
         <v>193</v>
@@ -1190,7 +1187,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
         <v>194</v>
@@ -1201,7 +1198,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
         <v>195</v>
@@ -1212,7 +1209,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
         <v>196</v>
@@ -1223,7 +1220,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
         <v>197</v>
@@ -1234,7 +1231,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1242,7 +1239,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1250,7 +1247,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1258,7 +1255,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1266,7 +1263,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1274,7 +1271,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1282,7 +1279,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1290,7 +1287,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
         <v>198</v>
@@ -1301,7 +1298,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
         <v>199</v>
@@ -1312,7 +1309,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1320,7 +1317,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1328,7 +1325,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
         <v>200</v>
@@ -1339,7 +1336,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1347,7 +1344,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1355,7 +1352,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1363,7 +1360,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1371,7 +1368,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1379,7 +1376,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1387,7 +1384,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
         <v>200</v>
@@ -1398,7 +1395,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1406,7 +1403,7 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
         <v>201</v>
@@ -1417,7 +1414,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1425,7 +1422,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1433,7 +1430,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1441,7 +1438,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1449,7 +1446,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1457,7 +1454,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1465,7 +1462,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1473,7 +1470,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
         <v>202</v>
@@ -1484,7 +1481,7 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
         <v>203</v>
@@ -1495,7 +1492,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1503,7 +1500,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1511,7 +1508,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1519,7 +1516,7 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C55" t="s">
         <v>204</v>
@@ -1530,7 +1527,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1538,7 +1535,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1546,7 +1543,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1554,7 +1551,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1562,7 +1559,7 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
         <v>205</v>
@@ -1573,7 +1570,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
+        <v>127</v>
+      </c>
+      <c r="C61" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1675,7 +1675,7 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C73" t="s">
         <v>192</v>
@@ -1686,7 +1686,7 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C74" t="s">
         <v>208</v>
@@ -1878,7 +1878,7 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
         <v>214</v>
@@ -1889,7 +1889,7 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C96" t="s">
         <v>215</v>
@@ -1900,7 +1900,7 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C97" t="s">
         <v>214</v>
@@ -1943,30 +1943,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
         <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="220">
   <si>
     <t>targa</t>
   </si>
@@ -371,316 +371,310 @@
     <t>MARSILI PAOLA</t>
   </si>
   <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1032,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1049,7 +1043,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1087,7 +1081,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1114,7 +1108,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1141,7 +1135,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1152,7 +1146,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1179,7 +1173,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1190,7 +1184,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1201,7 +1195,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1212,7 +1206,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1223,7 +1217,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1290,7 +1284,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1301,7 +1295,7 @@
         <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1328,7 +1322,7 @@
         <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1387,7 +1381,7 @@
         <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1406,7 +1400,7 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1473,7 +1467,7 @@
         <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1484,7 +1478,7 @@
         <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1519,7 +1513,7 @@
         <v>150</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1562,7 +1556,7 @@
         <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1573,7 +1567,7 @@
         <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1608,7 +1602,7 @@
         <v>159</v>
       </c>
       <c r="C65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1667,7 +1661,7 @@
         <v>166</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1678,7 +1672,7 @@
         <v>127</v>
       </c>
       <c r="C73" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1689,7 +1683,7 @@
         <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1700,7 +1694,7 @@
         <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1711,7 +1705,7 @@
         <v>168</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1738,7 +1732,7 @@
         <v>171</v>
       </c>
       <c r="C79" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1762,10 +1756,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1773,10 +1767,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C83" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1784,7 +1778,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1792,7 +1786,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1800,7 +1794,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1808,7 +1802,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1816,10 +1810,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1827,7 +1821,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1838,7 +1832,7 @@
         <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1846,7 +1840,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1854,7 +1848,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1862,7 +1856,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1870,7 +1864,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1881,7 +1875,7 @@
         <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1892,7 +1886,7 @@
         <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1903,7 +1897,7 @@
         <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1911,10 +1905,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C98" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -1929,44 +1923,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" t="s">
         <v>217</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>218</v>
-      </c>
-      <c r="C1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="219">
   <si>
     <t>targa</t>
   </si>
@@ -386,295 +386,292 @@
     <t>MARIA.LUCIANO</t>
   </si>
   <si>
+    <t>IN ATTESA SECONDA CHIAVE PER FINE RENT</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
     <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1029,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1043,7 +1040,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1081,7 +1078,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1108,7 +1105,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1135,7 +1132,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1146,7 +1143,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1173,7 +1170,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1184,7 +1181,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1195,7 +1192,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1206,7 +1203,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1217,7 +1214,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1251,6 +1248,9 @@
       <c r="B25" t="s">
         <v>123</v>
       </c>
+      <c r="C25" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
@@ -1397,10 +1397,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1408,7 +1408,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1416,7 +1416,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1424,7 +1424,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1432,7 +1432,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1440,7 +1440,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1456,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1464,10 +1464,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1475,10 +1475,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1486,7 +1486,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1494,7 +1494,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1502,7 +1502,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1510,10 +1510,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1521,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1529,7 +1529,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1537,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1545,7 +1545,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1553,10 +1553,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1567,7 +1567,7 @@
         <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1575,7 +1575,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1583,7 +1583,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1591,7 +1591,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1599,10 +1599,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1610,7 +1610,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1618,7 +1618,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1626,7 +1626,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1634,7 +1634,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1642,7 +1642,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1650,7 +1650,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1658,10 +1658,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1672,7 +1672,7 @@
         <v>127</v>
       </c>
       <c r="C73" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1683,7 +1683,7 @@
         <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1691,10 +1691,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1702,10 +1702,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1713,7 +1713,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1721,7 +1721,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1729,10 +1729,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1740,7 +1740,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1748,7 +1748,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1759,7 +1759,7 @@
         <v>127</v>
       </c>
       <c r="C82" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1767,10 +1767,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1778,7 +1778,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1786,7 +1786,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1794,7 +1794,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1802,7 +1802,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1810,7 +1810,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C88" t="s">
         <v>198</v>
@@ -1821,7 +1821,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1829,10 +1829,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="C90" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1840,7 +1840,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1848,7 +1848,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1856,7 +1856,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1864,7 +1864,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1875,7 +1875,7 @@
         <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1886,7 +1886,7 @@
         <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1897,7 +1897,7 @@
         <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1905,10 +1905,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C98" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -1918,35 +1918,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" t="s">
         <v>215</v>
-      </c>
-      <c r="B1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1954,13 +1954,69 @@
         <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
         <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>195</v>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="216">
   <si>
     <t>targa</t>
   </si>
@@ -548,130 +548,121 @@
     <t>SCACCIA FEDERICA</t>
   </si>
   <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1020,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1040,7 +1031,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1078,7 +1069,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1105,7 +1096,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1132,7 +1123,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1143,7 +1134,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1170,7 +1161,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1181,7 +1172,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1192,7 +1183,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1203,7 +1194,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1214,7 +1205,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1249,7 +1240,7 @@
         <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1284,7 +1275,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1295,7 +1286,7 @@
         <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1322,7 +1313,7 @@
         <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1381,7 +1372,7 @@
         <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1400,7 +1391,7 @@
         <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1467,7 +1458,7 @@
         <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1478,7 +1469,7 @@
         <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1513,7 +1504,7 @@
         <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1556,7 +1547,7 @@
         <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1567,7 +1558,7 @@
         <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1602,7 +1593,7 @@
         <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1661,7 +1652,7 @@
         <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1672,7 +1663,7 @@
         <v>127</v>
       </c>
       <c r="C73" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1683,7 +1674,7 @@
         <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1694,7 +1685,7 @@
         <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1705,7 +1696,7 @@
         <v>127</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1732,7 +1723,7 @@
         <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1759,7 +1750,7 @@
         <v>127</v>
       </c>
       <c r="C82" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1770,7 +1761,7 @@
         <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1810,10 +1801,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1821,7 +1812,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1829,10 +1820,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C90" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1840,7 +1831,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1848,7 +1839,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1856,7 +1847,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1864,7 +1855,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1875,7 +1866,7 @@
         <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1886,7 +1877,7 @@
         <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1897,7 +1888,7 @@
         <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1905,10 +1896,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -1918,105 +1909,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" t="s">
         <v>212</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>213</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>214</v>
-      </c>
-      <c r="D1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="217">
   <si>
     <t>targa</t>
   </si>
@@ -323,346 +323,349 @@
     <t>GRAVINA GIUSEPPE</t>
   </si>
   <si>
+    <t>IN ASSISTENZA (DAL 24-7) - FRIZIONE</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
+  </si>
+  <si>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>MARCHIONDA ILARIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>MARSILI PAOLA</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>IN ATTESA SECONDA CHIAVE PER FINE RENT</t>
+  </si>
+  <si>
     <t>STEFANO.CAMPLONE</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>MARCHIONDA ILARIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>MARSILI PAOLA</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>IN ATTESA SECONDA CHIAVE PER FINE RENT</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1023,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1031,7 +1034,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1041,6 +1044,9 @@
       <c r="B4" t="s">
         <v>102</v>
       </c>
+      <c r="C4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
@@ -1237,10 +1243,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1248,7 +1254,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1256,7 +1262,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1264,7 +1270,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1272,10 +1278,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1283,10 +1289,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1294,7 +1300,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1302,7 +1308,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1310,10 +1316,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1321,7 +1327,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1329,7 +1335,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1337,7 +1343,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1345,7 +1351,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1353,7 +1359,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1361,7 +1367,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1369,10 +1375,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1380,7 +1386,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1388,10 +1394,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1399,7 +1405,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1407,7 +1413,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1415,7 +1421,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1423,7 +1429,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1431,7 +1437,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1439,7 +1445,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1447,7 +1453,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1455,7 +1461,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
         <v>199</v>
@@ -1466,7 +1472,7 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
         <v>200</v>
@@ -1477,7 +1483,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1485,7 +1491,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1493,7 +1499,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1501,7 +1507,7 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
         <v>201</v>
@@ -1512,7 +1518,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1520,7 +1526,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1528,7 +1534,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1536,7 +1542,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1544,7 +1550,7 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
         <v>202</v>
@@ -1555,10 +1561,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1566,7 +1572,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1574,7 +1580,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1582,7 +1588,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1590,7 +1596,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
         <v>203</v>
@@ -1601,7 +1607,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1609,7 +1615,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1617,7 +1623,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1625,7 +1631,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1633,7 +1639,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1641,7 +1647,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1649,7 +1655,7 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C72" t="s">
         <v>204</v>
@@ -1660,7 +1666,7 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C73" t="s">
         <v>189</v>
@@ -1671,7 +1677,7 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" t="s">
         <v>205</v>
@@ -1682,7 +1688,7 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s">
         <v>206</v>
@@ -1693,10 +1699,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1704,7 +1710,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1712,7 +1718,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1720,7 +1726,7 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C79" t="s">
         <v>191</v>
@@ -1731,7 +1737,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1739,7 +1745,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1747,10 +1753,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1758,7 +1764,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C83" t="s">
         <v>207</v>
@@ -1769,7 +1775,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1777,7 +1783,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1785,7 +1791,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1793,7 +1799,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1804,7 +1810,7 @@
         <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1812,7 +1818,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1820,10 +1826,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C90" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1831,7 +1837,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1839,7 +1845,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1847,7 +1853,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1855,7 +1861,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1863,7 +1869,7 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C95" t="s">
         <v>208</v>
@@ -1874,7 +1880,7 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C96" t="s">
         <v>209</v>
@@ -1885,7 +1891,7 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C97" t="s">
         <v>208</v>
@@ -1896,7 +1902,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C98" t="s">
         <v>210</v>
@@ -1909,7 +1915,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1928,16 +1934,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
         <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="216">
   <si>
     <t>targa</t>
   </si>
@@ -545,6 +545,9 @@
     <t>SCACCIA FEDERICA</t>
   </si>
   <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
     <t>COCO.FEDERICO</t>
   </si>
   <si>
@@ -660,12 +663,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>IN ATTESA SECONDA CHIAVE PER FINE RENT</t>
-  </si>
-  <si>
-    <t>STEFANO.CAMPLONE</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1020,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1034,7 +1031,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1045,7 +1042,7 @@
         <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1075,7 +1072,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1102,7 +1099,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1129,7 +1126,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1140,7 +1137,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1167,7 +1164,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1178,7 +1175,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1189,7 +1186,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1200,7 +1197,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1211,7 +1208,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1246,7 +1243,7 @@
         <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1281,7 +1278,7 @@
         <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1292,7 +1289,7 @@
         <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1319,7 +1316,7 @@
         <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1378,7 +1375,7 @@
         <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1397,7 +1394,7 @@
         <v>126</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1464,7 +1461,7 @@
         <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1475,7 +1472,7 @@
         <v>144</v>
       </c>
       <c r="C51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1510,7 +1507,7 @@
         <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1553,7 +1550,7 @@
         <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1564,7 +1561,7 @@
         <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1599,7 +1596,7 @@
         <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1658,7 +1655,7 @@
         <v>164</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1669,7 +1666,7 @@
         <v>126</v>
       </c>
       <c r="C73" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1680,7 +1677,7 @@
         <v>126</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1691,7 +1688,7 @@
         <v>165</v>
       </c>
       <c r="C75" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1702,7 +1699,7 @@
         <v>126</v>
       </c>
       <c r="C76" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1729,7 +1726,7 @@
         <v>168</v>
       </c>
       <c r="C79" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1756,7 +1753,7 @@
         <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1767,7 +1764,7 @@
         <v>171</v>
       </c>
       <c r="C83" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1807,10 +1804,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="C88" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1818,7 +1815,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1826,10 +1823,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C90" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1837,7 +1834,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1845,7 +1842,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1853,7 +1850,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1861,7 +1858,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1872,7 +1869,7 @@
         <v>126</v>
       </c>
       <c r="C95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1883,7 +1880,7 @@
         <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1894,7 +1891,7 @@
         <v>126</v>
       </c>
       <c r="C97" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1902,10 +1899,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -1915,49 +1912,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="216">
   <si>
     <t>targa</t>
   </si>
@@ -317,352 +317,352 @@
     <t>GL352TJ</t>
   </si>
   <si>
+    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA (DAL 24-7) - FRIZIONE</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE</t>
   </si>
   <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA (DAL 24-7) - FRIZIONE</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>MARCHIONDA ILARIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>MARSILI PAOLA</t>
   </si>
   <si>
     <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>MARCHIONDA ILARIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>MARSILI PAOLA</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1020,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1031,7 +1031,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1042,7 +1042,7 @@
         <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1072,7 +1072,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1099,7 +1099,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1126,7 +1126,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1137,7 +1137,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1164,7 +1164,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1175,7 +1175,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1183,10 +1183,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1194,10 +1194,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1205,10 +1205,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1216,7 +1216,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1224,7 +1224,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1232,7 +1232,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1243,7 +1243,7 @@
         <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1251,7 +1251,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1259,7 +1259,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1267,7 +1267,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>112</v>
+      </c>
+      <c r="C28" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1275,10 +1278,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1286,10 +1289,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1297,7 +1300,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1305,7 +1308,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1313,10 +1316,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1324,7 +1327,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1332,7 +1335,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1340,7 +1343,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1348,7 +1351,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1356,7 +1359,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1364,7 +1367,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1372,10 +1375,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1383,7 +1386,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1391,10 +1394,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1402,7 +1405,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1410,7 +1413,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1418,7 +1421,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1426,7 +1429,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1434,7 +1437,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1442,7 +1445,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1450,7 +1453,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>112</v>
+      </c>
+      <c r="C49" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1458,10 +1464,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1469,10 +1475,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1480,7 +1486,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1488,7 +1494,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1496,7 +1502,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1504,10 +1510,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1515,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1523,7 +1529,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1531,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1539,7 +1545,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1547,10 +1553,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C60" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1558,10 +1564,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1569,7 +1575,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1577,7 +1583,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1585,7 +1591,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1593,10 +1599,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1604,7 +1610,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1612,7 +1618,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1620,7 +1626,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1628,7 +1634,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1636,7 +1642,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1644,7 +1650,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1652,10 +1658,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1663,10 +1669,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C73" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1674,10 +1680,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C74" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1685,10 +1691,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1696,10 +1702,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C76" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1707,7 +1713,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1715,7 +1721,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1723,10 +1729,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C79" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1734,7 +1740,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1742,7 +1748,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1750,10 +1756,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C82" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1761,10 +1767,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C83" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1772,7 +1778,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1780,7 +1786,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1788,7 +1794,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1796,7 +1802,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1804,10 +1810,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C88" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1815,7 +1821,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1823,10 +1829,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1834,7 +1840,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1842,7 +1848,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1850,7 +1856,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1858,7 +1864,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1866,10 +1872,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C95" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1877,10 +1883,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C96" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1888,10 +1894,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1899,10 +1905,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C98" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -1912,35 +1918,161 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" t="s">
         <v>100</v>
       </c>
-      <c r="C2" t="s">
-        <v>176</v>
-      </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="210">
   <si>
     <t>targa</t>
   </si>
@@ -323,66 +323,66 @@
     <t>GRAVINA GIUSEPPE</t>
   </si>
   <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>MARCHIONDA ILARIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
     <t>IN ASSISTENZA (DAL 24-7) - FRIZIONE</t>
   </si>
   <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>MARCHIONDA ILARIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
     <t>ELEONORA:PERINO</t>
   </si>
   <si>
@@ -566,30 +566,30 @@
     <t>2026-07-08</t>
   </si>
   <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
     <t>2026-07-24</t>
   </si>
   <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
     <t>2026-07-03</t>
   </si>
   <si>
@@ -645,24 +645,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>MARSILI PAOLA</t>
-  </si>
-  <si>
-    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1024,7 @@
         <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1072,7 +1054,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1099,7 +1081,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1126,7 +1108,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1134,7 +1116,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
         <v>181</v>
@@ -1145,7 +1127,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1153,7 +1135,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1161,10 +1143,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1172,10 +1154,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1183,7 +1165,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
         <v>181</v>
@@ -1194,10 +1176,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1205,10 +1187,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1216,7 +1198,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1224,7 +1206,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1232,7 +1214,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1240,10 +1222,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1267,7 +1249,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
         <v>181</v>
@@ -1453,7 +1435,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C49" t="s">
         <v>181</v>
@@ -1732,7 +1714,7 @@
         <v>165</v>
       </c>
       <c r="C79" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1813,7 +1795,7 @@
         <v>173</v>
       </c>
       <c r="C88" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1918,7 +1900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1937,141 +1919,15 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" t="s">
         <v>181</v>
       </c>
     </row>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="215">
   <si>
     <t>targa</t>
   </si>
@@ -353,6 +353,9 @@
     <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
   </si>
   <si>
+    <t>VOCIONE MICHELA</t>
+  </si>
+  <si>
     <t>CINZIA.D'ORAZIO</t>
   </si>
   <si>
@@ -365,6 +368,9 @@
     <t>MASCIARELLI MAURIZIO</t>
   </si>
   <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
     <t>BONFITTO DAVIDE</t>
   </si>
   <si>
@@ -380,271 +386,280 @@
     <t>MARIA.LUCIANO</t>
   </si>
   <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE È PRONTA AL RITIRO)</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
     <t>IN ASSISTENZA (DAL 24-7) - FRIZIONE</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1017,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1013,7 +1028,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1024,7 +1039,7 @@
         <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1054,7 +1069,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1081,7 +1096,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1108,7 +1123,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1116,10 +1131,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1127,7 +1142,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1135,7 +1150,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1143,10 +1158,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1154,10 +1169,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1165,10 +1180,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1176,10 +1191,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1187,10 +1202,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1198,7 +1213,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1206,7 +1221,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1214,7 +1229,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1222,10 +1237,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1233,7 +1248,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1241,7 +1256,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1249,10 +1264,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1260,10 +1275,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1271,10 +1286,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1282,7 +1297,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1290,7 +1305,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1298,10 +1313,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1309,7 +1324,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1317,7 +1332,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1325,7 +1340,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1333,7 +1348,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1341,7 +1356,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1349,7 +1364,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1357,10 +1372,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1368,7 +1383,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1376,10 +1391,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1387,7 +1402,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1395,7 +1410,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1403,7 +1418,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1411,7 +1426,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>102</v>
+      </c>
+      <c r="C46" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1419,7 +1437,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1427,7 +1445,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1435,10 +1453,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1446,10 +1464,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1457,10 +1475,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1468,7 +1486,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1476,7 +1494,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1484,7 +1502,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1492,10 +1510,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1503,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1511,7 +1529,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1519,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1527,7 +1545,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1535,10 +1553,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C60" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1546,10 +1564,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1557,7 +1575,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1565,7 +1583,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1573,7 +1591,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1581,10 +1599,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C65" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1592,7 +1610,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1600,7 +1618,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1608,7 +1626,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1616,7 +1634,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1624,7 +1642,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1632,7 +1650,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1640,10 +1658,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1651,10 +1669,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C73" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1662,10 +1680,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1673,10 +1691,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C75" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1684,10 +1702,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C76" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1695,7 +1713,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1703,7 +1721,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1711,10 +1729,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C79" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1722,7 +1740,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1730,7 +1748,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1738,10 +1756,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C82" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1749,10 +1767,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1760,7 +1778,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1768,7 +1786,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1776,7 +1794,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1784,7 +1802,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1792,10 +1810,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1803,7 +1821,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1811,10 +1829,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C90" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1822,7 +1840,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1830,7 +1848,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1838,7 +1856,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1846,7 +1864,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1854,10 +1872,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1865,10 +1883,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1876,10 +1894,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1887,10 +1905,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C98" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1900,35 +1918,105 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>213</v>
       </c>
       <c r="C2" t="s">
         <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="215">
   <si>
     <t>targa</t>
   </si>
@@ -323,343 +323,343 @@
     <t>GRAVINA GIUSEPPE</t>
   </si>
   <si>
+    <t>D'ORAZIO CINZIA</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VOCIONE MICHELA</t>
+  </si>
+  <si>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>MARCHIONDA ILARIA</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE</t>
   </si>
   <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VOCIONE MICHELA</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>MARCHIONDA ILARIA</t>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE È PRONTA AL RITIRO)</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
   </si>
   <si>
     <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE È PRONTA AL RITIRO)</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA (DAL 24-7) - FRIZIONE</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1039,7 @@
         <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1069,7 +1069,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1096,7 +1096,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1123,7 +1123,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1134,7 +1134,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1161,7 +1161,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1172,7 +1172,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1183,7 +1183,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1240,7 +1240,7 @@
         <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1267,7 +1267,7 @@
         <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1426,10 +1426,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1437,7 +1437,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1456,7 +1456,7 @@
         <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1464,7 +1464,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
         <v>197</v>
@@ -1475,7 +1475,7 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
         <v>198</v>
@@ -1486,7 +1486,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1494,7 +1494,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1502,7 +1502,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1510,7 +1510,7 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
         <v>199</v>
@@ -1521,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1529,7 +1529,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1537,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1545,7 +1545,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1553,7 +1553,7 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1583,7 +1583,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1591,7 +1591,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1599,7 +1599,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
         <v>183</v>
@@ -1610,7 +1610,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1618,7 +1618,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1626,7 +1626,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1634,7 +1634,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1642,7 +1642,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1650,7 +1650,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1658,7 +1658,7 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C72" t="s">
         <v>201</v>
@@ -1691,7 +1691,7 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s">
         <v>204</v>
@@ -1713,7 +1713,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1721,7 +1721,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1729,10 +1729,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C79" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1740,7 +1740,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1748,7 +1748,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1767,10 +1767,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1778,7 +1778,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1786,7 +1786,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1794,7 +1794,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1802,7 +1802,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1810,10 +1810,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="C88" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1875,7 +1875,7 @@
         <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1886,7 +1886,7 @@
         <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1897,7 +1897,7 @@
         <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1918,21 +1918,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1940,83 +1940,55 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
         <v>102</v>
       </c>
-      <c r="C5" t="s">
-        <v>117</v>
-      </c>
       <c r="D5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="215">
   <si>
     <t>targa</t>
   </si>
@@ -356,310 +356,310 @@
     <t>VOCIONE MICHELA</t>
   </si>
   <si>
+    <t>CENTRO DAMA (DA PORTARE IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>MARCHIONDA ILARIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE È PRONTA AL RITIRO)</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>MARCHIONDA ILARIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE È PRONTA AL RITIRO)</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
   </si>
 </sst>
 </file>
@@ -1144,6 +1144,9 @@
       <c r="B15" t="s">
         <v>113</v>
       </c>
+      <c r="C15" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
@@ -1918,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1937,57 +1940,15 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" t="s">
         <v>185</v>
       </c>
     </row>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="214">
   <si>
     <t>targa</t>
   </si>
@@ -362,304 +362,301 @@
     <t>DI TIZIO.VALENTINA</t>
   </si>
   <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>MARCHIONDA ILARIA</t>
   </si>
   <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
     <t>IN ASSISTENZA ( POI DA ASSEGNARE È PRONTA AL RITIRO)</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1014,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1028,7 +1025,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1039,7 +1036,7 @@
         <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1069,7 +1066,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1096,7 +1093,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1123,7 +1120,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1134,7 +1131,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1145,7 +1142,7 @@
         <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1164,7 +1161,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1172,10 +1169,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1183,10 +1180,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1194,10 +1191,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1205,10 +1202,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1216,7 +1213,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1224,7 +1221,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1232,7 +1229,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1240,7 +1237,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
         <v>189</v>
@@ -1251,7 +1248,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1259,7 +1256,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1267,10 +1264,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1278,10 +1275,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1289,10 +1286,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1300,7 +1297,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1308,7 +1305,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1316,10 +1313,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1327,7 +1324,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1335,7 +1332,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1343,7 +1340,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1351,7 +1348,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1359,7 +1356,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1367,7 +1364,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1375,10 +1372,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1386,7 +1383,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1394,10 +1391,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1405,7 +1402,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1413,7 +1410,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1421,7 +1418,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1429,10 +1426,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1440,7 +1437,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1448,7 +1445,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1456,10 +1453,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1467,10 +1464,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1478,10 +1475,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C51" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1489,7 +1486,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1497,7 +1494,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1505,7 +1502,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1513,10 +1510,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1524,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1532,7 +1529,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1540,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1548,7 +1545,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1556,10 +1553,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C60" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1567,10 +1564,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1578,7 +1575,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1586,7 +1583,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1594,7 +1591,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1602,10 +1599,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1613,7 +1610,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1621,7 +1618,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1629,7 +1626,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1637,7 +1634,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1645,7 +1642,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1653,7 +1650,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1661,10 +1658,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1672,10 +1669,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C73" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1683,10 +1680,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1694,10 +1691,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C75" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1705,10 +1702,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1716,7 +1713,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1724,7 +1721,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1732,10 +1729,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C79" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1743,7 +1740,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1751,7 +1748,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1759,10 +1756,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1770,10 +1767,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1781,7 +1778,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1789,7 +1786,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1797,7 +1794,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1805,7 +1802,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1813,10 +1810,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C88" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1824,7 +1821,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1832,10 +1829,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C90" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1843,7 +1840,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1851,7 +1848,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1859,7 +1856,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1867,7 +1864,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1875,10 +1872,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C95" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1886,10 +1883,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1897,10 +1894,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C97" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1908,10 +1905,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
+        <v>181</v>
+      </c>
+      <c r="C98" t="s">
         <v>182</v>
-      </c>
-      <c r="C98" t="s">
-        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1921,35 +1918,63 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" t="s">
         <v>210</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>211</v>
-      </c>
-      <c r="C1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_212AD31869035161965DD44B4D31505C3301D54A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6022CC27-0D90-4897-86DB-021D19230898}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="216">
   <si>
     <t>targa</t>
   </si>
@@ -657,16 +663,22 @@
   </si>
   <si>
     <t>IN ASSISTENZA ( POI DA ASSEGNARE È PRONTA AL RITIRO)</t>
+  </si>
+  <si>
+    <t>HE418NR</t>
+  </si>
+  <si>
+    <t>HE929WB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -700,17 +712,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -748,7 +768,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -782,6 +802,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -816,9 +837,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -991,11 +1013,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C100"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="66.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1017,7 +1043,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1028,7 +1054,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1039,7 +1065,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1047,7 +1073,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1058,7 +1084,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1069,7 +1095,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1077,7 +1103,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1085,7 +1111,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1096,7 +1122,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1104,7 +1130,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1112,7 +1138,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1123,7 +1149,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1160,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1145,7 +1171,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1153,7 +1179,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1164,7 +1190,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1175,7 +1201,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1186,7 +1212,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1197,7 +1223,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1208,7 +1234,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1216,7 +1242,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1224,7 +1250,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1232,7 +1258,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1243,7 +1269,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1251,7 +1277,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1259,7 +1285,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1270,7 +1296,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1281,7 +1307,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1292,7 +1318,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1300,7 +1326,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1308,7 +1334,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1319,7 +1345,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1327,7 +1353,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1335,7 +1361,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1343,7 +1369,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1351,7 +1377,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1385,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1367,7 +1393,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1378,7 +1404,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1386,7 +1412,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1397,7 +1423,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1405,7 +1431,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1413,7 +1439,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1421,7 +1447,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1432,7 +1458,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1440,7 +1466,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1448,7 +1474,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1459,7 +1485,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1470,7 +1496,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1481,7 +1507,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1489,7 +1515,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -1497,7 +1523,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -1505,7 +1531,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1516,7 +1542,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1524,7 +1550,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1532,7 +1558,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1540,7 +1566,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -1548,7 +1574,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1559,7 +1585,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1570,7 +1596,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1578,7 +1604,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -1586,7 +1612,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -1594,7 +1620,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -1605,7 +1631,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -1613,7 +1639,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -1621,7 +1647,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -1629,7 +1655,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -1637,7 +1663,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -1645,7 +1671,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -1653,7 +1679,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -1664,7 +1690,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -1675,7 +1701,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -1686,7 +1712,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -1697,7 +1723,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -1708,7 +1734,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -1716,7 +1742,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -1724,7 +1750,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -1735,7 +1761,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -1743,7 +1769,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -1751,7 +1777,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -1762,7 +1788,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -1773,7 +1799,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -1781,7 +1807,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -1789,7 +1815,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -1797,7 +1823,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -1805,7 +1831,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -1816,7 +1842,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -1824,7 +1850,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -1835,7 +1861,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -1843,7 +1869,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -1851,7 +1877,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -1859,7 +1885,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -1867,7 +1893,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -1878,7 +1904,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -1889,7 +1915,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -1900,7 +1926,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -1909,6 +1935,16 @@
       </c>
       <c r="C98" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -1917,11 +1953,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>208</v>
       </c>
@@ -1935,7 +1971,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1949,7 +1985,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1963,7 +1999,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_212AD31869035161965DD44B4D31505C3301D54A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6022CC27-0D90-4897-86DB-021D19230898}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="217">
   <si>
     <t>targa</t>
   </si>
@@ -323,6 +317,12 @@
     <t>GL352TJ</t>
   </si>
   <si>
+    <t>HE418NR</t>
+  </si>
+  <si>
+    <t>HE929WB</t>
+  </si>
+  <si>
     <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
   </si>
   <si>
@@ -536,149 +536,146 @@
     <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
   </si>
   <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>VALERIO.D'ANTONIO</t>
   </si>
   <si>
     <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>MARCHIONDA ILARIA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE È PRONTA AL RITIRO)</t>
-  </si>
-  <si>
-    <t>HE418NR</t>
-  </si>
-  <si>
-    <t>HE929WB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -712,25 +709,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -768,7 +757,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -802,7 +791,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -837,10 +825,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1013,15 +1000,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="66.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1032,790 +1015,796 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1">
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C46" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C73" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C74" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C82" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="C84" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="C85" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -1823,7 +1812,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -1831,18 +1820,18 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -1850,7 +1839,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -1858,10 +1847,10 @@
         <v>176</v>
       </c>
       <c r="C90" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -1869,7 +1858,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -1877,7 +1866,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -1885,7 +1874,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -1893,40 +1882,40 @@
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C95" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C96" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C97" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -1934,17 +1923,29 @@
         <v>181</v>
       </c>
       <c r="C98" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C99" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>215</v>
+        <v>101</v>
+      </c>
+      <c r="B100" t="s">
+        <v>183</v>
+      </c>
+      <c r="C100" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -1953,64 +1954,72 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_483AB11D69D35B7F26EE53360975CD1E2A4D9219" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B54F9FFB-15C1-44AB-810C-AF9981D50A77}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -671,11 +677,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -709,17 +715,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -757,7 +771,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -791,6 +805,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -825,9 +840,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1000,11 +1016,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1015,7 +1031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1026,7 +1042,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1037,7 +1053,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1048,7 +1064,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1056,7 +1072,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1067,7 +1083,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1078,7 +1094,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1086,7 +1102,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1094,7 +1110,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1105,7 +1121,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1113,7 +1129,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1121,7 +1137,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1132,7 +1148,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1143,7 +1159,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1154,7 +1170,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1162,7 +1178,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1173,7 +1189,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1184,7 +1200,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1195,7 +1211,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1206,7 +1222,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1217,7 +1233,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1225,7 +1241,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1233,7 +1249,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1241,7 +1257,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1252,7 +1268,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1260,7 +1276,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1268,7 +1284,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1279,7 +1295,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1290,7 +1306,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1301,7 +1317,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1309,7 +1325,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1317,7 +1333,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1328,7 +1344,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1336,7 +1352,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1344,7 +1360,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1352,7 +1368,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1360,7 +1376,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1368,7 +1384,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1376,7 +1392,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1387,7 +1403,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1395,7 +1411,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1406,7 +1422,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1414,7 +1430,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1422,7 +1438,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1430,7 +1446,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1441,7 +1457,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1449,7 +1465,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1457,18 +1473,18 @@
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C49" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1479,7 +1495,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1490,7 +1506,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1498,7 +1514,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -1506,7 +1522,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -1514,7 +1530,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1525,7 +1541,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1533,7 +1549,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1541,7 +1557,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1549,7 +1565,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -1557,7 +1573,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1568,7 +1584,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1579,7 +1595,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1587,7 +1603,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -1595,7 +1611,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -1603,7 +1619,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -1614,7 +1630,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -1622,7 +1638,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -1630,7 +1646,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -1638,7 +1654,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -1646,7 +1662,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -1654,7 +1670,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -1662,7 +1678,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -1673,7 +1689,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -1684,7 +1700,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -1695,7 +1711,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -1706,7 +1722,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -1717,7 +1733,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -1725,7 +1741,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -1733,7 +1749,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -1744,7 +1760,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -1752,7 +1768,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -1760,7 +1776,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -1771,7 +1787,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -1782,7 +1798,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -1793,7 +1809,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -1804,7 +1820,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -1812,7 +1828,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -1820,7 +1836,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -1831,7 +1847,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -1839,7 +1855,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -1850,7 +1866,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -1858,7 +1874,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -1866,7 +1882,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -1874,7 +1890,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -1882,7 +1898,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -1893,7 +1909,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -1904,7 +1920,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -1915,7 +1931,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -1926,7 +1942,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>100</v>
       </c>
@@ -1937,7 +1953,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>101</v>
       </c>
@@ -1954,11 +1970,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>211</v>
       </c>
@@ -1972,7 +1988,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1986,7 +2002,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -2000,7 +2016,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -2011,7 +2027,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>101</v>
       </c>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_483AB11D69D35B7F26EE53360975CD1E2A4D9219" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B54F9FFB-15C1-44AB-810C-AF9981D50A77}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="217">
   <si>
     <t>targa</t>
   </si>
@@ -368,320 +362,320 @@
     <t>VOCIONE MICHELA</t>
   </si>
   <si>
+    <t>IN ASSISTENZA</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA (PRONTA)</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>CENTRO DAMA (DA PORTARE IN ASSISTENZA)</t>
   </si>
   <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
     <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,25 +709,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -771,7 +757,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -805,7 +791,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -840,10 +825,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1016,11 +1000,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1042,7 +1026,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1037,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1064,7 +1048,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1072,7 +1056,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1083,7 +1067,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1094,7 +1078,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1102,7 +1086,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1110,7 +1094,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1121,7 +1105,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1129,7 +1113,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1137,7 +1121,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1148,7 +1132,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1159,7 +1143,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1167,10 +1151,10 @@
         <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1178,7 +1162,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1186,362 +1170,362 @@
         <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C46" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1549,7 +1533,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1557,7 +1541,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1565,7 +1549,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -1573,7 +1557,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1584,18 +1568,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1603,7 +1587,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -1611,7 +1595,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -1619,7 +1603,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -1630,7 +1614,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -1638,7 +1622,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -1646,7 +1630,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -1654,7 +1638,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -1662,7 +1646,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -1670,7 +1654,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -1678,7 +1662,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -1689,29 +1673,29 @@
         <v>201</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C74" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -1722,18 +1706,18 @@
         <v>204</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -1741,7 +1725,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -1749,7 +1733,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -1760,7 +1744,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -1768,7 +1752,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -1776,18 +1760,18 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -1798,29 +1782,29 @@
         <v>206</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C84" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C85" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -1828,7 +1812,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -1836,18 +1820,18 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C88" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -1855,7 +1839,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -1863,10 +1847,10 @@
         <v>176</v>
       </c>
       <c r="C90" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -1874,7 +1858,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -1882,7 +1866,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -1890,7 +1874,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -1898,40 +1882,40 @@
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C95" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C96" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C97" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -1942,7 +1926,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>100</v>
       </c>
@@ -1953,7 +1937,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>101</v>
       </c>
@@ -1970,11 +1954,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>211</v>
       </c>
@@ -1988,54 +1972,60 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
         <v>215</v>
       </c>
-      <c r="C2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
         <v>216</v>
       </c>
-      <c r="C3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_3826511569C3DF5A5E1ECB07DD36911B1C75D3D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7F855B-6A8E-4BBE-94D1-80F19C8F492A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -452,9 +458,6 @@
     <t>LORELLAD'ORTONA</t>
   </si>
   <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
     <t>IN ASSISTENZA (PRONTA)</t>
   </si>
   <si>
@@ -666,16 +669,19 @@
   </si>
   <si>
     <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>MELANY MA VA IN ASSISTENZA REVISIONE PRIMA SETTIMANA DI SETTEMBRE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -709,17 +715,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -757,7 +771,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -791,6 +805,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -825,9 +840,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1000,11 +1016,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1015,7 +1031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1023,10 +1039,10 @@
         <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1034,10 +1050,10 @@
         <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1045,10 +1061,10 @@
         <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1056,7 +1072,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1067,7 +1083,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1075,10 +1091,10 @@
         <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1086,7 +1102,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1094,7 +1110,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1102,10 +1118,10 @@
         <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1113,7 +1129,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1121,7 +1137,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1129,10 +1145,10 @@
         <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1140,10 +1156,10 @@
         <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1151,10 +1167,10 @@
         <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1162,7 +1178,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1170,21 +1186,21 @@
         <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>216</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1192,10 +1208,10 @@
         <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1203,10 +1219,10 @@
         <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1214,10 +1230,10 @@
         <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1225,7 +1241,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1233,7 +1249,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1241,7 +1257,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1249,10 +1265,10 @@
         <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1260,7 +1276,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1268,7 +1284,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1276,10 +1292,10 @@
         <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1287,10 +1303,10 @@
         <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1298,10 +1314,10 @@
         <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1309,7 +1325,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1317,7 +1333,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1325,10 +1341,10 @@
         <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1336,7 +1352,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1344,7 +1360,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1352,7 +1368,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1360,7 +1376,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1368,7 +1384,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1376,7 +1392,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1384,10 +1400,10 @@
         <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1395,7 +1411,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1403,10 +1419,10 @@
         <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1414,7 +1430,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1422,7 +1438,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1430,7 +1446,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1438,10 +1454,10 @@
         <v>143</v>
       </c>
       <c r="C46" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1449,7 +1465,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1457,7 +1473,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1465,56 +1481,56 @@
         <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1522,53 +1538,53 @@
         <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1576,104 +1592,104 @@
         <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -1681,10 +1697,10 @@
         <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -1692,21 +1708,21 @@
         <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -1714,53 +1730,53 @@
         <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C79" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -1768,21 +1784,21 @@
         <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C83" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -1790,10 +1806,10 @@
         <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -1801,26 +1817,26 @@
         <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -1828,61 +1844,61 @@
         <v>143</v>
       </c>
       <c r="C88" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -1890,10 +1906,10 @@
         <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -1901,10 +1917,10 @@
         <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -1912,40 +1928,40 @@
         <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C99" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C100" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1954,25 +1970,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" t="s">
         <v>211</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>212</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>213</v>
       </c>
-      <c r="D1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1980,41 +1996,41 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C3" t="s">
         <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C4" t="s">
         <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2025,7 +2041,7 @@
         <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_3826511569C3DF5A5E1ECB07DD36911B1C75D3D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7F855B-6A8E-4BBE-94D1-80F19C8F492A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="219">
   <si>
     <t>targa</t>
   </si>
@@ -368,320 +362,326 @@
     <t>VOCIONE MICHELA</t>
   </si>
   <si>
+    <t>IN ASSISTENA (PRONTA AL RITIRO - 28/08/26)</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>MELANY MA VA IN ASSISTENZA REVISIONE PRIMA SETTIMANA DI SETTEMBRE</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>KALOV - TEMPORANEO, LA SUA IN ASSISTENZA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA (È DI KALOV)</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>IN ASSISTENZA</t>
   </si>
   <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
+    <t>KALOV SLAVI KRASIMIROV</t>
   </si>
   <si>
     <t>IN ASSISTENZA (PRONTA)</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>CENTRO DAMA (DA PORTARE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>MELANY MA VA IN ASSISTENZA REVISIONE PRIMA SETTIMANA DI SETTEMBRE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,25 +715,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -771,7 +763,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -805,7 +797,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -840,10 +831,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1016,11 +1006,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1039,10 +1029,10 @@
         <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1050,10 +1040,10 @@
         <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1061,10 +1051,10 @@
         <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1072,7 +1062,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1083,7 +1073,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1091,10 +1081,10 @@
         <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1102,7 +1092,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1110,7 +1100,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1118,10 +1108,10 @@
         <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1129,7 +1119,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1137,7 +1127,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1145,10 +1135,10 @@
         <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1156,10 +1146,10 @@
         <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1167,10 +1157,10 @@
         <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1178,7 +1168,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1186,21 +1176,21 @@
         <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1208,10 +1198,10 @@
         <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1219,10 +1209,10 @@
         <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1230,10 +1220,10 @@
         <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1241,7 +1231,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1249,7 +1239,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1257,7 +1247,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1265,10 +1255,10 @@
         <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1276,7 +1266,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1284,7 +1274,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1292,10 +1282,10 @@
         <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1303,10 +1293,10 @@
         <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1314,10 +1304,10 @@
         <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1325,7 +1315,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1333,7 +1323,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1341,10 +1331,10 @@
         <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1352,7 +1342,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1360,7 +1350,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1368,7 +1358,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1376,7 +1366,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1384,7 +1374,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1392,7 +1382,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1400,10 +1390,10 @@
         <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1411,7 +1401,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1419,10 +1409,10 @@
         <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1430,7 +1420,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1438,7 +1428,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1446,7 +1436,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1454,10 +1444,10 @@
         <v>143</v>
       </c>
       <c r="C46" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1465,7 +1455,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1473,7 +1463,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1481,56 +1471,56 @@
         <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1538,53 +1528,53 @@
         <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1592,104 +1582,104 @@
         <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -1697,10 +1687,10 @@
         <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -1708,21 +1698,21 @@
         <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -1730,53 +1720,53 @@
         <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -1784,21 +1774,21 @@
         <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -1806,10 +1796,10 @@
         <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -1817,26 +1807,26 @@
         <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -1844,61 +1834,64 @@
         <v>143</v>
       </c>
       <c r="C88" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C90" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="C94" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -1906,10 +1899,10 @@
         <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -1917,10 +1910,10 @@
         <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -1928,40 +1921,40 @@
         <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C98" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C99" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C100" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -1970,78 +1963,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>52</v>
       </c>
-      <c r="B2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>56</v>
-      </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="218">
   <si>
     <t>targa</t>
   </si>
@@ -434,244 +434,241 @@
     <t>ESTER.FECONDO</t>
   </si>
   <si>
+    <t>KALOV - TEMPORANEO LA MACCHINA LA USERA' MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA 28/08/26</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA (È DI KALOV)</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>KALOV - TEMPORANEO, LA SUA IN ASSISTENZA</t>
+  </si>
+  <si>
     <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>KALOV - TEMPORANEO, LA SUA IN ASSISTENZA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA (È DI KALOV)</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA (PRONTA)</t>
   </si>
 </sst>
 </file>
@@ -1400,6 +1397,9 @@
       <c r="B41" t="s">
         <v>139</v>
       </c>
+      <c r="C41" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
@@ -1964,7 +1964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1983,13 +1983,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
         <v>216</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
         <v>191</v>
@@ -1997,29 +1997,15 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
         <v>217</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" t="s">
         <v>191</v>
       </c>
     </row>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="217">
   <si>
     <t>targa</t>
   </si>
@@ -323,352 +323,349 @@
     <t>HE929WB</t>
   </si>
   <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>D'ORAZIO CINZIA</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VOCIONE MICHELA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA (PRONTA AL RITIRO - 28/08/26)</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>MELANY MA VA IN ASSISTENZA REVISIONE PRIMA SETTIMANA DI SETTEMBRE</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>KALOV - TEMPORANEO LA MACCHINA LA USERA' MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA 28/08/26</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA (È DI KALOV)</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>D'ORAZIO CINZIA</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VOCIONE MICHELA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA (PRONTA AL RITIRO - 28/08/26)</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>MELANY MA VA IN ASSISTENZA REVISIONE PRIMA SETTIMANA DI SETTEMBRE</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>KALOV - TEMPORANEO LA MACCHINA LA USERA' MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA 28/08/26</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA (È DI KALOV)</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>KALOV - TEMPORANEO, LA SUA IN ASSISTENZA</t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1023,7 @@
         <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1037,7 +1034,7 @@
         <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1048,7 +1045,7 @@
         <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1078,7 +1075,7 @@
         <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1105,7 +1102,7 @@
         <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1132,7 +1129,7 @@
         <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1143,7 +1140,7 @@
         <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1154,7 +1151,7 @@
         <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1170,10 +1167,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1181,10 +1178,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1192,10 +1189,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1203,10 +1200,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1214,10 +1211,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1225,7 +1222,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1233,7 +1230,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1241,7 +1238,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1249,10 +1246,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1260,7 +1257,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1268,7 +1265,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1276,10 +1273,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1287,10 +1284,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1298,10 +1295,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1309,7 +1306,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1317,7 +1314,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1325,10 +1322,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1336,7 +1333,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1344,7 +1341,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1352,7 +1349,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1360,7 +1357,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1368,7 +1365,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1376,7 +1373,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1384,10 +1381,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1395,10 +1392,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1406,10 +1403,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1417,7 +1414,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1425,7 +1422,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1433,7 +1430,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1441,10 +1438,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1452,7 +1449,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1460,7 +1457,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1468,10 +1465,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1479,10 +1476,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1490,10 +1487,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1501,7 +1498,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1509,7 +1506,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1517,7 +1514,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1525,10 +1522,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C55" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1536,7 +1533,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1544,7 +1541,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1552,7 +1549,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1560,7 +1557,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1568,10 +1565,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1579,10 +1576,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1590,7 +1587,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1598,7 +1595,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1606,7 +1603,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1614,10 +1611,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1625,7 +1622,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1633,7 +1630,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1641,7 +1638,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1649,7 +1646,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1657,7 +1654,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1665,7 +1662,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1673,7 +1670,7 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C72" t="s">
         <v>202</v>
@@ -1684,7 +1681,7 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C73" t="s">
         <v>203</v>
@@ -1695,7 +1692,7 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C74" t="s">
         <v>204</v>
@@ -1706,7 +1703,7 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s">
         <v>205</v>
@@ -1717,10 +1714,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C76" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1728,7 +1725,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1736,7 +1733,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1744,7 +1741,7 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C79" t="s">
         <v>206</v>
@@ -1755,7 +1752,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1763,7 +1760,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1771,10 +1768,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1782,7 +1779,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C83" t="s">
         <v>207</v>
@@ -1793,7 +1790,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C84" t="s">
         <v>208</v>
@@ -1804,7 +1801,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C85" t="s">
         <v>208</v>
@@ -1815,7 +1812,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1823,7 +1820,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1831,7 +1828,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C88" t="s">
         <v>209</v>
@@ -1842,7 +1839,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1850,10 +1847,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1861,7 +1858,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1869,7 +1866,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1877,7 +1874,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1885,10 +1882,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1896,7 +1893,7 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C95" t="s">
         <v>210</v>
@@ -1907,7 +1904,7 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C96" t="s">
         <v>211</v>
@@ -1918,7 +1915,7 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C97" t="s">
         <v>210</v>
@@ -1929,10 +1926,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1940,7 +1937,7 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C99" t="s">
         <v>208</v>
@@ -1951,7 +1948,7 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C100" t="s">
         <v>208</v>
@@ -1964,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1983,30 +1980,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>216</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="218">
   <si>
     <t>targa</t>
   </si>
@@ -554,118 +554,121 @@
     <t>COMPARELLI</t>
   </si>
   <si>
+    <t>IN ASSISTENZA - PRONTA AL RITIRO - KALOV AVVISATO</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>IN ASSISTENA (È DI KALOV)</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1888,7 @@
         <v>179</v>
       </c>
       <c r="C94" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1896,7 +1899,7 @@
         <v>128</v>
       </c>
       <c r="C95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1907,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1918,7 +1921,7 @@
         <v>128</v>
       </c>
       <c r="C97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1966,30 +1969,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="220">
   <si>
     <t>targa</t>
   </si>
@@ -368,6 +368,9 @@
     <t>DI TIZIO.VALENTINA</t>
   </si>
   <si>
+    <t>IN ASSISTENZA - REVISIONE --&gt; DOPO SI PUO' ASSEGNARE</t>
+  </si>
+  <si>
     <t>MELANY MA VA IN ASSISTENZA REVISIONE PRIMA SETTIMANA DI SETTEMBRE</t>
   </si>
   <si>
@@ -452,223 +455,226 @@
     <t>NOD PESCARA</t>
   </si>
   <si>
+    <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA AL RITIRO - KALOV AVVISATO</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>IN ASSISTENZA - PRONTA 28/08/26</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA AL RITIRO - KALOV AVVISATO</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA (È DI KALOV)</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1032,7 @@
         <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1037,7 +1043,7 @@
         <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1048,7 +1054,7 @@
         <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1078,7 +1084,7 @@
         <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1105,7 +1111,7 @@
         <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1132,7 +1138,7 @@
         <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1143,7 +1149,7 @@
         <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1154,7 +1160,7 @@
         <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1170,10 +1176,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1181,10 +1187,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1192,10 +1198,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1203,10 +1209,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1214,10 +1220,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1225,7 +1231,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1233,7 +1239,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1241,7 +1247,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1249,10 +1255,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1260,7 +1266,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1268,7 +1274,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1276,10 +1282,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1287,10 +1293,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1298,10 +1304,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1309,7 +1315,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1317,7 +1323,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1325,10 +1331,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1336,7 +1342,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1344,7 +1350,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1352,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1360,7 +1366,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1368,7 +1374,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1376,7 +1382,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1384,10 +1390,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1395,10 +1401,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1406,10 +1412,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1417,7 +1423,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1425,7 +1431,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1433,7 +1439,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1441,10 +1447,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1452,7 +1458,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1460,7 +1466,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1468,10 +1474,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1479,10 +1485,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1490,10 +1496,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1501,7 +1507,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1509,7 +1515,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1517,7 +1523,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1525,10 +1531,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1536,7 +1542,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1544,7 +1550,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1552,7 +1558,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1560,7 +1566,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1568,10 +1574,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1579,10 +1585,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1590,7 +1596,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1598,7 +1604,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1606,7 +1612,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1614,10 +1620,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1625,7 +1631,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1633,7 +1639,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1641,7 +1647,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1649,7 +1655,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1657,7 +1663,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1665,7 +1671,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1673,10 +1679,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1684,10 +1690,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1695,10 +1701,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1706,10 +1712,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1717,10 +1723,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1728,7 +1734,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1736,7 +1742,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1744,10 +1750,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1755,7 +1761,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1763,7 +1769,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1771,10 +1777,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1782,10 +1788,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1793,10 +1799,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1804,10 +1810,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1815,7 +1821,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1823,7 +1829,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1831,10 +1837,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C88" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1842,7 +1848,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1850,10 +1856,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C90" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1861,7 +1867,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1869,7 +1875,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1877,7 +1883,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1885,10 +1891,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C94" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1896,10 +1902,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1907,10 +1913,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1918,10 +1924,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1929,10 +1935,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C98" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1940,10 +1946,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C99" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1951,10 +1957,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C100" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -1964,35 +1970,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="222">
   <si>
     <t>targa</t>
   </si>
@@ -371,310 +371,316 @@
     <t>IN ASSISTENZA - REVISIONE --&gt; DOPO SI PUO' ASSEGNARE</t>
   </si>
   <si>
+    <t>DE LUCA ALESSIA - LA PRENDE TEMPORANEO . LA LASCIA DOPO PER REVISIONE</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA LA DEVE RIPRENDERE MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>KALOV - TEMPORANEO LA MACCHINA LA USERA' MELANY</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA AL RITIRO - KALOV AVVISATO</t>
+  </si>
+  <si>
     <t>MELANY MA VA IN ASSISTENZA REVISIONE PRIMA SETTIMANA DI SETTEMBRE</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>KALOV - TEMPORANEO LA MACCHINA LA USERA' MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA AL RITIRO - KALOV AVVISATO</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA 28/08/26</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1410,7 @@
         <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1534,7 +1540,7 @@
         <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1577,7 +1583,7 @@
         <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1623,7 +1629,7 @@
         <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1682,7 +1688,7 @@
         <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1693,7 +1699,7 @@
         <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1704,7 +1710,7 @@
         <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1715,7 +1721,7 @@
         <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1753,7 +1759,7 @@
         <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1791,7 +1797,7 @@
         <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1802,7 +1808,7 @@
         <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1813,7 +1819,7 @@
         <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1840,7 +1846,7 @@
         <v>143</v>
       </c>
       <c r="C88" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1894,7 +1900,7 @@
         <v>180</v>
       </c>
       <c r="C94" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1938,7 +1944,7 @@
         <v>181</v>
       </c>
       <c r="C98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1949,7 +1955,7 @@
         <v>182</v>
       </c>
       <c r="C99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1960,7 +1966,7 @@
         <v>183</v>
       </c>
       <c r="C100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -1970,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1989,30 +1995,44 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="221">
   <si>
     <t>targa</t>
   </si>
@@ -368,319 +368,316 @@
     <t>DI TIZIO.VALENTINA</t>
   </si>
   <si>
+    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
+  </si>
+  <si>
+    <t>DE LUCA ALESSIA - LA PRENDE TEMPORANEO . LA LASCIA DOPO PER REVISIONE</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA LA DEVE RIPRENDERE MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>IN ASSISTENZA - REVISIONE --&gt; DOPO SI PUO' ASSEGNARE</t>
-  </si>
-  <si>
-    <t>DE LUCA ALESSIA - LA PRENDE TEMPORANEO . LA LASCIA DOPO PER REVISIONE</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA LA DEVE RIPRENDERE MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>KALOV - TEMPORANEO LA MACCHINA LA USERA' MELANY</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA AL RITIRO - KALOV AVVISATO</t>
-  </si>
-  <si>
-    <t>MELANY MA VA IN ASSISTENZA REVISIONE PRIMA SETTIMANA DI SETTEMBRE</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1502,7 @@
         <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1540,7 +1537,7 @@
         <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1583,7 +1580,7 @@
         <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1629,7 +1626,7 @@
         <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1688,7 +1685,7 @@
         <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1699,7 +1696,7 @@
         <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1710,7 +1707,7 @@
         <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1721,7 +1718,7 @@
         <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1759,7 +1756,7 @@
         <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1797,7 +1794,7 @@
         <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1808,7 +1805,7 @@
         <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1819,7 +1816,7 @@
         <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1846,7 +1843,7 @@
         <v>143</v>
       </c>
       <c r="C88" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1911,7 +1908,7 @@
         <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1922,7 +1919,7 @@
         <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1933,7 +1930,7 @@
         <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1944,7 +1941,7 @@
         <v>181</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1955,7 +1952,7 @@
         <v>182</v>
       </c>
       <c r="C99" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1966,7 +1963,7 @@
         <v>183</v>
       </c>
       <c r="C100" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -1976,63 +1973,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="223">
   <si>
     <t>targa</t>
   </si>
@@ -362,322 +362,328 @@
     <t>VOCIONE MICHELA</t>
   </si>
   <si>
+    <t>DA ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA LA DEVE RIPRENDERE MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>DE LUCA ALESSIA</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>IN ASSISTENA (PRONTA AL RITIRO - 28/08/26)</t>
   </si>
   <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
-  </si>
-  <si>
     <t>DE LUCA ALESSIA - LA PRENDE TEMPORANEO . LA LASCIA DOPO PER REVISIONE</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA LA DEVE RIPRENDERE MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - REVISIONE --&gt; DOPO SI PUO' ASSEGNARE</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1041,7 @@
         <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1046,7 +1052,7 @@
         <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1057,7 +1063,7 @@
         <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1087,7 +1093,7 @@
         <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1114,7 +1120,7 @@
         <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1141,7 +1147,7 @@
         <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1152,7 +1158,7 @@
         <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1163,7 +1169,7 @@
         <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1182,7 +1188,7 @@
         <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1193,7 +1199,7 @@
         <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1204,7 +1210,7 @@
         <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1288,7 +1294,7 @@
         <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1407,7 +1413,7 @@
         <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1418,7 +1424,7 @@
         <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1453,7 +1459,7 @@
         <v>143</v>
       </c>
       <c r="C46" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1480,7 +1486,7 @@
         <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1491,7 +1497,7 @@
         <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1502,7 +1508,7 @@
         <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1537,7 +1543,7 @@
         <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1580,7 +1586,7 @@
         <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1591,7 +1597,7 @@
         <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1626,7 +1632,7 @@
         <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1685,7 +1691,7 @@
         <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1696,7 +1702,7 @@
         <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1707,7 +1713,7 @@
         <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1718,7 +1724,7 @@
         <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1729,7 +1735,7 @@
         <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1756,7 +1762,7 @@
         <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1783,7 +1789,7 @@
         <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1794,7 +1800,7 @@
         <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1805,7 +1811,7 @@
         <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1816,7 +1822,7 @@
         <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1840,10 +1846,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1851,7 +1857,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1859,10 +1865,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1870,7 +1876,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1878,7 +1884,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1886,7 +1892,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1894,10 +1900,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C94" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1908,7 +1914,7 @@
         <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1919,7 +1925,7 @@
         <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1930,7 +1936,7 @@
         <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1938,10 +1944,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C98" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1949,10 +1955,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C99" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1960,10 +1966,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -1973,34 +1979,62 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" t="s">
         <v>192</v>
       </c>
     </row>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{E2103A9E-C155-420D-8FFF-DD946158B8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3019D61-02A0-458A-890E-936DC596FA5B}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="228">
   <si>
     <t>targa</t>
   </si>
@@ -684,16 +690,31 @@
   </si>
   <si>
     <t>DE LUCA ALESSIA - LA PRENDE TEMPORANEO . LA LASCIA DOPO PER REVISIONE</t>
+  </si>
+  <si>
+    <t>HC323JD</t>
+  </si>
+  <si>
+    <t>HC877LT</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>modello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,17 +748,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -775,7 +804,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -809,6 +838,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -843,9 +873,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1018,11 +1049,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D102"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1032,8 +1066,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1044,7 +1081,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1055,7 +1092,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1066,7 +1103,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1074,7 +1111,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1085,7 +1122,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1096,7 +1133,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1104,7 +1141,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1112,7 +1149,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1123,7 +1160,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1131,7 +1168,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1139,7 +1176,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1150,7 +1187,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1161,7 +1198,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1172,7 +1209,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1180,7 +1217,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1191,7 +1228,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1202,7 +1239,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1213,7 +1250,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1224,7 +1261,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1235,7 +1272,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1243,7 +1280,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1251,7 +1288,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1259,7 +1296,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1270,7 +1307,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1278,7 +1315,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1286,7 +1323,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1297,7 +1334,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1308,7 +1345,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1319,7 +1356,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1327,7 +1364,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1335,7 +1372,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1346,7 +1383,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1354,7 +1391,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1362,7 +1399,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1370,7 +1407,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1378,7 +1415,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1386,7 +1423,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1394,7 +1431,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1405,7 +1442,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1416,7 +1453,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1427,7 +1464,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1435,7 +1472,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1443,7 +1480,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1451,7 +1488,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1462,7 +1499,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1470,7 +1507,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1478,7 +1515,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1489,7 +1526,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1500,7 +1537,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1511,7 +1548,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1519,7 +1556,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -1527,7 +1564,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -1535,7 +1572,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1546,7 +1583,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1554,7 +1591,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1562,7 +1599,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1570,7 +1607,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -1578,7 +1615,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1589,7 +1626,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1600,7 +1637,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1608,7 +1645,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -1616,7 +1653,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -1624,7 +1661,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -1635,7 +1672,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -1643,7 +1680,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -1651,7 +1688,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -1659,7 +1696,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -1667,7 +1704,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -1675,7 +1712,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -1683,7 +1720,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -1694,7 +1731,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -1705,7 +1742,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -1716,7 +1753,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -1727,7 +1764,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -1738,7 +1775,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -1746,7 +1783,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -1754,7 +1791,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -1765,7 +1802,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -1773,7 +1810,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -1781,7 +1818,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -1792,7 +1829,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -1803,7 +1840,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -1814,7 +1851,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -1825,7 +1862,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -1833,7 +1870,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -1841,7 +1878,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -1852,7 +1889,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -1860,7 +1897,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -1871,7 +1908,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -1879,7 +1916,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -1887,7 +1924,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -1895,7 +1932,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -1906,7 +1943,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -1917,7 +1954,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -1928,7 +1965,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -1939,7 +1976,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -1950,7 +1987,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>100</v>
       </c>
@@ -1961,7 +1998,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>101</v>
       </c>
@@ -1970,6 +2007,28 @@
       </c>
       <c r="C100" t="s">
         <v>213</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" t="s">
+        <v>225</v>
+      </c>
+      <c r="D101" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>224</v>
+      </c>
+      <c r="B102" t="s">
+        <v>225</v>
+      </c>
+      <c r="D102" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -1978,11 +2037,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>217</v>
       </c>
@@ -1996,7 +2055,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2010,7 +2069,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -2024,7 +2083,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>47</v>
       </c>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_7B32331169F35B3756ECD176CD396C5B1B39A1E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11026D88-2EAF-411F-A2D6-08DC59A033E6}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -443,9 +449,6 @@
     <t>ESTER.FECONDO</t>
   </si>
   <si>
-    <t>IN ASSISTENZA - PRONTA LA DEVE RIPRENDERE MELANY</t>
-  </si>
-  <si>
     <t>DIEGO.PANTALONE</t>
   </si>
   <si>
@@ -702,16 +705,19 @@
   </si>
   <si>
     <t>IN ASSISTENZA - PRONTA</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,17 +751,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -793,7 +807,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -827,6 +841,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -861,9 +876,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1036,11 +1052,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1062,10 +1081,10 @@
         <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1073,10 +1092,10 @@
         <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1084,10 +1103,10 @@
         <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1095,7 +1114,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1106,7 +1125,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1114,10 +1133,10 @@
         <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1125,7 +1144,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1133,7 +1152,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1141,10 +1160,10 @@
         <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1152,7 +1171,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1160,7 +1179,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1168,10 +1187,10 @@
         <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1179,10 +1198,10 @@
         <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1190,10 +1209,10 @@
         <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1201,7 +1220,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1209,10 +1228,10 @@
         <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1220,10 +1239,10 @@
         <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1231,10 +1250,10 @@
         <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1242,10 +1261,10 @@
         <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1253,10 +1272,10 @@
         <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1264,7 +1283,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1272,7 +1291,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1280,7 +1299,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1288,10 +1307,10 @@
         <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1299,7 +1318,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1307,7 +1326,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1315,10 +1334,10 @@
         <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1326,10 +1345,10 @@
         <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1337,10 +1356,10 @@
         <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -1348,7 +1367,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -1356,7 +1375,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -1364,10 +1383,10 @@
         <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1375,7 +1394,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1383,7 +1402,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1391,7 +1410,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1399,7 +1418,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1407,7 +1426,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1415,7 +1434,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1423,21 +1442,21 @@
         <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="C41" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1445,53 +1464,53 @@
         <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1499,7 +1518,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1507,56 +1526,56 @@
         <v>132</v>
       </c>
       <c r="C49" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -1564,53 +1583,53 @@
         <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -1618,104 +1637,104 @@
         <v>132</v>
       </c>
       <c r="C61" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C65" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -1723,10 +1742,10 @@
         <v>132</v>
       </c>
       <c r="C73" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -1734,21 +1753,21 @@
         <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>77</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C75" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -1756,53 +1775,53 @@
         <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C79" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
       <c r="B80" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -1810,21 +1829,21 @@
         <v>132</v>
       </c>
       <c r="C82" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C83" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -1832,10 +1851,10 @@
         <v>132</v>
       </c>
       <c r="C84" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -1843,91 +1862,91 @@
         <v>132</v>
       </c>
       <c r="C85" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>89</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>91</v>
       </c>
       <c r="B89" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>92</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C90" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>94</v>
       </c>
       <c r="B92" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>95</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C94" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -1935,10 +1954,10 @@
         <v>132</v>
       </c>
       <c r="C95" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -1946,10 +1965,10 @@
         <v>132</v>
       </c>
       <c r="C96" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -1957,62 +1976,62 @@
         <v>132</v>
       </c>
       <c r="C97" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>100</v>
       </c>
       <c r="B98" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C98" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>101</v>
       </c>
       <c r="B99" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C99" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>102</v>
       </c>
       <c r="B100" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C100" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>103</v>
       </c>
       <c r="B101" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D101" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>104</v>
       </c>
       <c r="B102" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D102" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2021,53 +2040,53 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" t="s">
         <v>223</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>224</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>225</v>
       </c>
-      <c r="D1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
         <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2078,7 +2097,7 @@
         <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -8,20 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_7B32331169F35B3756ECD176CD396C5B1B39A1E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11026D88-2EAF-411F-A2D6-08DC59A033E6}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{A1DB1996-044F-4014-ACCD-361D83DB1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84776238-8DD4-49CA-8A9A-EEAB79A350F1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stato Attuale'!$A$1:$E$105</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="241">
   <si>
     <t>targa</t>
   </si>
@@ -440,9 +443,6 @@
     <t>FELICIA.FALCONIO</t>
   </si>
   <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
     <t>PIERPAOLO.ALEMANNO</t>
   </si>
   <si>
@@ -708,6 +708,45 @@
   </si>
   <si>
     <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>HC441JD</t>
+  </si>
+  <si>
+    <t>HC428JD</t>
+  </si>
+  <si>
+    <t>HC442JD</t>
   </si>
 </sst>
 </file>
@@ -1053,13 +1092,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D102"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1072,8 +1113,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1081,10 +1125,10 @@
         <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1092,10 +1136,13 @@
         <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="E3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1103,18 +1150,24 @@
         <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="E4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1124,8 +1177,11 @@
       <c r="C6" s="1">
         <v>45851</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1133,26 +1189,32 @@
         <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1160,26 +1222,35 @@
         <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="E10" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1187,10 +1258,10 @@
         <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1198,10 +1269,10 @@
         <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1209,18 +1280,24 @@
         <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1228,10 +1305,10 @@
         <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1239,10 +1316,13 @@
         <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="E18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1250,10 +1330,10 @@
         <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1261,10 +1341,13 @@
         <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="E20" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1272,34 +1355,46 @@
         <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="E21" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1307,26 +1402,35 @@
         <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="E25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1334,10 +1438,13 @@
         <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="E28" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1345,10 +1452,10 @@
         <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1356,26 +1463,35 @@
         <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="E30" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -1383,58 +1499,76 @@
         <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
       <c r="B35" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
       <c r="B36" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="E37" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="E38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="E39" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1442,21 +1576,24 @@
         <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C41" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1464,53 +1601,68 @@
         <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="E43" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="E44" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="E45" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="E46" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="E47" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1518,7 +1670,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1526,56 +1678,65 @@
         <v>132</v>
       </c>
       <c r="C49" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="E52" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="E53" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="E54" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -1583,53 +1744,65 @@
         <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="E56" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="E57" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E58" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="E59" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -1637,104 +1810,137 @@
         <v>132</v>
       </c>
       <c r="C61" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="E62" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
       <c r="B63" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="E63" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="E64" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C65" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="E65" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="E66" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="E67" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="E68" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="E69" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="E70" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="E71" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C72" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="E72" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -1742,10 +1948,10 @@
         <v>132</v>
       </c>
       <c r="C73" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -1753,21 +1959,24 @@
         <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>77</v>
       </c>
       <c r="B75" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="E75" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -1775,53 +1984,65 @@
         <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="E77" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="E78" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="E80" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="E81" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -1829,21 +2050,24 @@
         <v>132</v>
       </c>
       <c r="C82" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="E83" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -1851,10 +2075,10 @@
         <v>132</v>
       </c>
       <c r="C84" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -1862,91 +2086,118 @@
         <v>132</v>
       </c>
       <c r="C85" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="E86" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>89</v>
       </c>
       <c r="B87" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="E87" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C88" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="E88" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>91</v>
       </c>
       <c r="B89" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="E89" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>92</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C90" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="E90" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+      <c r="E91" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>94</v>
       </c>
       <c r="B92" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="E92" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>95</v>
       </c>
       <c r="B93" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="E93" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C94" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="E94" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -1954,10 +2205,10 @@
         <v>132</v>
       </c>
       <c r="C95" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -1965,10 +2216,10 @@
         <v>132</v>
       </c>
       <c r="C96" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -1976,65 +2227,116 @@
         <v>132</v>
       </c>
       <c r="C97" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>100</v>
       </c>
       <c r="B98" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="E98" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>101</v>
       </c>
       <c r="B99" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C99" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+      <c r="E99" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>102</v>
       </c>
       <c r="B100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C100" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+      <c r="E100" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>103</v>
       </c>
       <c r="B101" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D101" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>104</v>
       </c>
       <c r="B102" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D102" t="s">
-        <v>221</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>238</v>
+      </c>
+      <c r="B103" t="s">
+        <v>186</v>
+      </c>
+      <c r="D103" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>239</v>
+      </c>
+      <c r="B104" t="s">
+        <v>186</v>
+      </c>
+      <c r="D104" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>240</v>
+      </c>
+      <c r="B105" t="s">
+        <v>186</v>
+      </c>
+      <c r="D105" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E105" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters blank="1">
+        <filter val="SANGRO AVENTINO"/>
+        <filter val="VASTO"/>
+        <filter val="VASTO COSTA SUD"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2046,16 +2348,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" t="s">
         <v>222</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>223</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>224</v>
-      </c>
-      <c r="D1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2063,13 +2365,13 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
         <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2077,13 +2379,13 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2097,7 +2399,7 @@
         <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{A1DB1996-044F-4014-ACCD-361D83DB1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84776238-8DD4-49CA-8A9A-EEAB79A350F1}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{A1DB1996-044F-4014-ACCD-361D83DB1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF6F68E2-2579-4DBA-82DE-4A23FE9361EE}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stato Attuale'!$A$1:$E$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stato Attuale'!$A$1:$E$88</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="219">
   <si>
     <t>targa</t>
   </si>
@@ -119,9 +119,6 @@
     <t>GL325TJ</t>
   </si>
   <si>
-    <t>GL326TJ</t>
-  </si>
-  <si>
     <t>GL327TJ</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t>GL332TJ</t>
   </si>
   <si>
-    <t>GL333TJ</t>
-  </si>
-  <si>
     <t>GL335TJ</t>
   </si>
   <si>
@@ -152,15 +146,9 @@
     <t>GL345TJ</t>
   </si>
   <si>
-    <t>GL346TJ</t>
-  </si>
-  <si>
     <t>GL347TJ</t>
   </si>
   <si>
-    <t>GL350TJ</t>
-  </si>
-  <si>
     <t>GL351TJ</t>
   </si>
   <si>
@@ -176,12 +164,6 @@
     <t>GL359TJ</t>
   </si>
   <si>
-    <t>GL368TJ</t>
-  </si>
-  <si>
-    <t>GL369TJ</t>
-  </si>
-  <si>
     <t>GL370TJ</t>
   </si>
   <si>
@@ -197,9 +179,6 @@
     <t>GL376TJ</t>
   </si>
   <si>
-    <t>GL377TJ</t>
-  </si>
-  <si>
     <t>GL378TJ</t>
   </si>
   <si>
@@ -215,9 +194,6 @@
     <t>GL383TJ</t>
   </si>
   <si>
-    <t>GL385TJ</t>
-  </si>
-  <si>
     <t>GL388TJ</t>
   </si>
   <si>
@@ -251,18 +227,9 @@
     <t>GL590TH</t>
   </si>
   <si>
-    <t>GL591TH</t>
-  </si>
-  <si>
-    <t>GL592TH</t>
-  </si>
-  <si>
     <t>GL593TH</t>
   </si>
   <si>
-    <t>GL594TH</t>
-  </si>
-  <si>
     <t>GL595TH</t>
   </si>
   <si>
@@ -278,18 +245,9 @@
     <t>GL748TH</t>
   </si>
   <si>
-    <t>GL757TH</t>
-  </si>
-  <si>
     <t>GT751SR</t>
   </si>
   <si>
-    <t>GM448BL</t>
-  </si>
-  <si>
-    <t>GM598BL</t>
-  </si>
-  <si>
     <t>GT039LP</t>
   </si>
   <si>
@@ -317,15 +275,6 @@
     <t>GZ093WW</t>
   </si>
   <si>
-    <t>GX834SK</t>
-  </si>
-  <si>
-    <t>GY983FY</t>
-  </si>
-  <si>
-    <t>GX666SK</t>
-  </si>
-  <si>
     <t>GL352TJ</t>
   </si>
   <si>
@@ -422,9 +371,6 @@
     <t>SELLINI CRISTAL</t>
   </si>
   <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
     <t>CINOSI MELANIA</t>
   </si>
   <si>
@@ -536,9 +482,6 @@
     <t>SABINA.LANCIA</t>
   </si>
   <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
     <t>IEZZI.SERENA</t>
   </si>
   <si>
@@ -623,15 +566,9 @@
     <t>2026-08-20</t>
   </si>
   <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
     <t>2026-06-01</t>
   </si>
   <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
     <t>2026-09-07</t>
   </si>
   <si>
@@ -647,9 +584,6 @@
     <t>2026-09-02</t>
   </si>
   <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
     <t>2025-12-19</t>
   </si>
   <si>
@@ -659,12 +593,6 @@
     <t>2026-03-09</t>
   </si>
   <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
     <t>2026-02-25</t>
   </si>
   <si>
@@ -680,12 +608,6 @@
     <t>2026-07-24</t>
   </si>
   <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
     <t xml:space="preserve">pandina </t>
   </si>
   <si>
@@ -747,6 +669,18 @@
   </si>
   <si>
     <t>HC442JD</t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
   </si>
 </sst>
 </file>
@@ -1092,12 +1026,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1114,7 +1049,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1122,10 +1057,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>168</v>
+      </c>
+      <c r="E2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1133,13 +1071,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1147,13 +1085,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1161,24 +1099,24 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1">
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1186,21 +1124,24 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="E7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1208,10 +1149,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1219,13 +1160,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1233,21 +1174,21 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1255,10 +1196,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>173</v>
+      </c>
+      <c r="E13" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1266,35 +1210,38 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="E14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E15" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1302,24 +1249,27 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="E17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1327,24 +1277,27 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="E19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="E20" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1352,24 +1305,24 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E21" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1377,10 +1330,10 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1388,60 +1341,60 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="E25" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="E28" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1449,46 +1402,46 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="E29" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" t="s">
-        <v>200</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1496,21 +1449,21 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
-      </c>
-      <c r="C33" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="E33" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1518,10 +1471,10 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1529,32 +1482,35 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>237</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>201</v>
+      </c>
+      <c r="C38" t="s">
+        <v>181</v>
       </c>
       <c r="E38" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1562,10 +1518,10 @@
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E39" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1573,24 +1529,21 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>227</v>
-      </c>
-      <c r="C41" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1598,57 +1551,63 @@
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="E42" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E43" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>128</v>
+      </c>
+      <c r="C44" t="s">
+        <v>184</v>
       </c>
       <c r="E44" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>129</v>
+      </c>
+      <c r="C45" t="s">
+        <v>185</v>
       </c>
       <c r="E45" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
-      </c>
-      <c r="C46" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="E46" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1656,10 +1615,10 @@
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E47" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1669,16 +1628,19 @@
       <c r="B48" t="s">
         <v>132</v>
       </c>
+      <c r="E48" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" t="s">
-        <v>195</v>
+        <v>133</v>
+      </c>
+      <c r="E49" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,10 +1648,10 @@
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" t="s">
-        <v>205</v>
+        <v>134</v>
+      </c>
+      <c r="E50" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1697,21 +1659,21 @@
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" t="s">
+        <v>135</v>
+      </c>
+      <c r="E51" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1719,21 +1681,21 @@
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
-      </c>
-      <c r="E53" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="C53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E54" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1741,10 +1703,10 @@
         <v>57</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
-      </c>
-      <c r="C55" t="s">
-        <v>207</v>
+        <v>139</v>
+      </c>
+      <c r="E55" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1752,10 +1714,10 @@
         <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E56" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1763,21 +1725,24 @@
         <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
+        <v>141</v>
+      </c>
+      <c r="C57" t="s">
+        <v>187</v>
       </c>
       <c r="E57" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E58" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1785,10 +1750,10 @@
         <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="E59" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1796,10 +1761,10 @@
         <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
-      </c>
-      <c r="C60" t="s">
-        <v>208</v>
+        <v>144</v>
+      </c>
+      <c r="E60" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1807,21 +1772,21 @@
         <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
-      </c>
-      <c r="C61" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="E61" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E62" t="s">
-        <v>235</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1829,21 +1794,24 @@
         <v>65</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E63" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="C64" t="s">
+        <v>188</v>
       </c>
       <c r="E64" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -1851,35 +1819,35 @@
         <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C65" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="E65" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E66" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E67" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -1887,21 +1855,24 @@
         <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>218</v>
+      </c>
+      <c r="C68" t="s">
+        <v>190</v>
       </c>
       <c r="E68" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E69" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -1909,35 +1880,35 @@
         <v>72</v>
       </c>
       <c r="B70" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E70" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>154</v>
+      </c>
+      <c r="C71" t="s">
+        <v>191</v>
       </c>
       <c r="E71" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
-      </c>
-      <c r="C72" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="E72" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -1945,10 +1916,10 @@
         <v>75</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
-      </c>
-      <c r="C73" t="s">
-        <v>211</v>
+        <v>156</v>
+      </c>
+      <c r="E73" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -1956,10 +1927,13 @@
         <v>76</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="C74" t="s">
-        <v>212</v>
+        <v>193</v>
+      </c>
+      <c r="E74" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -1967,13 +1941,10 @@
         <v>77</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
-      </c>
-      <c r="C75" t="s">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="E75" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -1981,10 +1952,13 @@
         <v>78</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>203</v>
+        <v>182</v>
+      </c>
+      <c r="E76" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -1992,21 +1966,21 @@
         <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E77" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E78" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2014,21 +1988,24 @@
         <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
-      </c>
-      <c r="C79" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="E79" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>163</v>
+      </c>
+      <c r="C80" t="s">
+        <v>181</v>
       </c>
       <c r="E80" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2036,10 +2013,13 @@
         <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>172</v>
+        <v>164</v>
+      </c>
+      <c r="C81" t="s">
+        <v>187</v>
       </c>
       <c r="E81" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2047,24 +2027,33 @@
         <v>84</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="C82" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="D82" t="s">
+        <v>217</v>
+      </c>
+      <c r="E82" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>215</v>
+        <v>192</v>
+      </c>
+      <c r="D83" t="s">
+        <v>217</v>
       </c>
       <c r="E83" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2072,10 +2061,10 @@
         <v>86</v>
       </c>
       <c r="B84" t="s">
-        <v>132</v>
-      </c>
-      <c r="C84" t="s">
-        <v>216</v>
+        <v>167</v>
+      </c>
+      <c r="D84" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2083,260 +2072,47 @@
         <v>87</v>
       </c>
       <c r="B85" t="s">
-        <v>132</v>
-      </c>
-      <c r="C85" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="D85" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
-      </c>
-      <c r="E86" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="D86" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
-      </c>
-      <c r="E87" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="D87" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>214</v>
       </c>
       <c r="B88" t="s">
-        <v>176</v>
-      </c>
-      <c r="C88" t="s">
-        <v>217</v>
-      </c>
-      <c r="E88" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>91</v>
-      </c>
-      <c r="B89" t="s">
-        <v>177</v>
-      </c>
-      <c r="E89" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>92</v>
-      </c>
-      <c r="B90" t="s">
-        <v>178</v>
-      </c>
-      <c r="C90" t="s">
-        <v>203</v>
-      </c>
-      <c r="E90" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>93</v>
-      </c>
-      <c r="B91" t="s">
-        <v>179</v>
-      </c>
-      <c r="E91" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>94</v>
-      </c>
-      <c r="B92" t="s">
-        <v>180</v>
-      </c>
-      <c r="E92" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>95</v>
-      </c>
-      <c r="B93" t="s">
-        <v>181</v>
-      </c>
-      <c r="E93" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>96</v>
-      </c>
-      <c r="B94" t="s">
-        <v>182</v>
-      </c>
-      <c r="C94" t="s">
-        <v>202</v>
-      </c>
-      <c r="E94" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>97</v>
-      </c>
-      <c r="B95" t="s">
-        <v>132</v>
-      </c>
-      <c r="C95" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>98</v>
-      </c>
-      <c r="B96" t="s">
-        <v>132</v>
-      </c>
-      <c r="C96" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>99</v>
-      </c>
-      <c r="B97" t="s">
-        <v>132</v>
-      </c>
-      <c r="C97" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>100</v>
-      </c>
-      <c r="B98" t="s">
-        <v>183</v>
-      </c>
-      <c r="C98" t="s">
-        <v>209</v>
-      </c>
-      <c r="E98" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>101</v>
-      </c>
-      <c r="B99" t="s">
-        <v>184</v>
-      </c>
-      <c r="C99" t="s">
-        <v>216</v>
-      </c>
-      <c r="E99" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>102</v>
-      </c>
-      <c r="B100" t="s">
-        <v>185</v>
-      </c>
-      <c r="C100" t="s">
-        <v>216</v>
-      </c>
-      <c r="E100" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>103</v>
-      </c>
-      <c r="B101" t="s">
-        <v>186</v>
-      </c>
-      <c r="D101" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>104</v>
-      </c>
-      <c r="B102" t="s">
-        <v>186</v>
-      </c>
-      <c r="D102" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>238</v>
-      </c>
-      <c r="B103" t="s">
-        <v>186</v>
-      </c>
-      <c r="D103" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>239</v>
-      </c>
-      <c r="B104" t="s">
-        <v>186</v>
-      </c>
-      <c r="D104" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>240</v>
-      </c>
-      <c r="B105" t="s">
-        <v>186</v>
-      </c>
-      <c r="D105" t="s">
-        <v>220</v>
+        <v>167</v>
+      </c>
+      <c r="D88" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E105" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters blank="1">
-        <filter val="SANGRO AVENTINO"/>
-        <filter val="VASTO"/>
-        <filter val="VASTO COSTA SUD"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E88" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2348,16 +2124,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="B1" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="C1" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="D1" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2365,13 +2141,13 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2379,13 +2155,13 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2393,13 +2169,13 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{A1DB1996-044F-4014-ACCD-361D83DB1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF6F68E2-2579-4DBA-82DE-4A23FE9361EE}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{A1DB1996-044F-4014-ACCD-361D83DB1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C53134F-E518-43B9-8786-F84F637E9664}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10335" yWindow="1230" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="222">
   <si>
     <t>targa</t>
   </si>
@@ -681,6 +681,15 @@
   </si>
   <si>
     <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>HC460JD</t>
+  </si>
+  <si>
+    <t>HC547JD</t>
+  </si>
+  <si>
+    <t>HC653JD</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2108,6 +2117,39 @@
         <v>167</v>
       </c>
       <c r="D88" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" t="s">
+        <v>167</v>
+      </c>
+      <c r="D89" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>220</v>
+      </c>
+      <c r="B90" t="s">
+        <v>167</v>
+      </c>
+      <c r="D90" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>221</v>
+      </c>
+      <c r="B91" t="s">
+        <v>167</v>
+      </c>
+      <c r="D91" t="s">
         <v>194</v>
       </c>
     </row>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{A1DB1996-044F-4014-ACCD-361D83DB1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C53134F-E518-43B9-8786-F84F637E9664}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{A1DB1996-044F-4014-ACCD-361D83DB1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5170441-7073-413A-AB19-D4F8689603F6}"/>
   <bookViews>
-    <workbookView xWindow="10335" yWindow="1230" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="225">
   <si>
     <t>targa</t>
   </si>
@@ -690,6 +690,15 @@
   </si>
   <si>
     <t>HC653JD</t>
+  </si>
+  <si>
+    <t>HC437JD</t>
+  </si>
+  <si>
+    <t>HC577JE</t>
+  </si>
+  <si>
+    <t>HC837LT</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2150,6 +2159,39 @@
         <v>167</v>
       </c>
       <c r="D91" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>222</v>
+      </c>
+      <c r="B92" t="s">
+        <v>167</v>
+      </c>
+      <c r="D92" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>223</v>
+      </c>
+      <c r="B93" t="s">
+        <v>167</v>
+      </c>
+      <c r="D93" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>224</v>
+      </c>
+      <c r="B94" t="s">
+        <v>167</v>
+      </c>
+      <c r="D94" t="s">
         <v>194</v>
       </c>
     </row>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{A1DB1996-044F-4014-ACCD-361D83DB1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5170441-7073-413A-AB19-D4F8689603F6}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_379AD31B69D3DC1D1DEB0C401987C39C1C55DA14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92DF37C9-C731-4BF4-B546-05A1B436E7BB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,12 @@
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stato Attuale'!$A$1:$E$88</definedName>
-  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="228">
   <si>
     <t>targa</t>
   </si>
@@ -38,6 +35,9 @@
     <t>modello</t>
   </si>
   <si>
+    <t>nod</t>
+  </si>
+  <si>
     <t>GE457XW</t>
   </si>
   <si>
@@ -290,415 +290,421 @@
     <t>HC877LT</t>
   </si>
   <si>
+    <t>HC441JD</t>
+  </si>
+  <si>
+    <t>HC428JD</t>
+  </si>
+  <si>
+    <t>HC442JD</t>
+  </si>
+  <si>
+    <t>HC460JD</t>
+  </si>
+  <si>
+    <t>HC547JD</t>
+  </si>
+  <si>
+    <t>HC653JD</t>
+  </si>
+  <si>
+    <t>HC437JD</t>
+  </si>
+  <si>
+    <t>HC577JE</t>
+  </si>
+  <si>
+    <t>HC837LT</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE</t>
   </si>
   <si>
+    <t>CENTRO DAMA - DA PORTARE DA PASQUARELLI</t>
+  </si>
+  <si>
+    <t>D'ORAZIO CINZIA</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
+  </si>
+  <si>
+    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
+  </si>
+  <si>
+    <t>VOCIONE MICHELA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>DE LUCA ALESSIA</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
     <t>GRAVINA GIUSEPPE</t>
   </si>
   <si>
-    <t>D'ORAZIO CINZIA</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
-  </si>
-  <si>
-    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
-  </si>
-  <si>
-    <t>VOCIONE MICHELA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>DE LUCA ALESSIA</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
   </si>
   <si>
     <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
   </si>
   <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>HC441JD</t>
-  </si>
-  <si>
-    <t>HC428JD</t>
-  </si>
-  <si>
-    <t>HC442JD</t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>HC460JD</t>
-  </si>
-  <si>
-    <t>HC547JD</t>
-  </si>
-  <si>
-    <t>HC653JD</t>
-  </si>
-  <si>
-    <t>HC437JD</t>
-  </si>
-  <si>
-    <t>HC577JE</t>
-  </si>
-  <si>
-    <t>HC837LT</t>
+    <t>HC431JD</t>
+  </si>
+  <si>
+    <t>HC634JD</t>
+  </si>
+  <si>
+    <t>HC713JD</t>
+  </si>
+  <si>
+    <t>HC393JD</t>
+  </si>
+  <si>
+    <t>HC599JE</t>
   </si>
 </sst>
 </file>
@@ -1044,13 +1050,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1067,1199 +1070,1239 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>202</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="1">
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E10" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E15" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E18" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="E19" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="E20" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E25" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="E28" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E29" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E31" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>211</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="E38" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E41" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E42" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="E43" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E44" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E45" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E47" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E52" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C53" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E54" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E55" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E56" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E57" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E58" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E59" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="E60" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="E61" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E62" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E63" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C64" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="E64" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C65" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E65" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="E66" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E67" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="C68" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E68" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E69" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E70" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C71" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E71" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E72" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E73" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E74" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E75" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="E76" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="E77" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="E79" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C80" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="E80" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C81" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D82" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E82" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D83" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E83" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D84" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D85" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>212</v>
+        <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D86" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>213</v>
+        <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D87" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D88" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>219</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D89" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D90" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>221</v>
+        <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D91" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>222</v>
+        <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D92" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>223</v>
+        <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D93" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" t="s">
+        <v>180</v>
+      </c>
+      <c r="D94" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>223</v>
+      </c>
+      <c r="B95" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>224</v>
       </c>
-      <c r="B94" t="s">
-        <v>167</v>
-      </c>
-      <c r="D94" t="s">
-        <v>194</v>
+      <c r="B96" t="s">
+        <v>180</v>
+      </c>
+      <c r="D96" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>225</v>
+      </c>
+      <c r="B97" t="s">
+        <v>180</v>
+      </c>
+      <c r="D97" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>226</v>
+      </c>
+      <c r="B98" t="s">
+        <v>180</v>
+      </c>
+      <c r="D98" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>227</v>
+      </c>
+      <c r="B99" t="s">
+        <v>180</v>
+      </c>
+      <c r="D99" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E88" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="B1" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C1" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D1" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_379AD31B69D3DC1D1DEB0C401987C39C1C55DA14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92DF37C9-C731-4BF4-B546-05A1B436E7BB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="230">
   <si>
     <t>targa</t>
   </si>
@@ -317,6 +311,21 @@
     <t>HC837LT</t>
   </si>
   <si>
+    <t>HC431JD</t>
+  </si>
+  <si>
+    <t>HC634JD</t>
+  </si>
+  <si>
+    <t>HC713JD</t>
+  </si>
+  <si>
+    <t>HC393JD</t>
+  </si>
+  <si>
+    <t>HC599JE</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE</t>
   </si>
   <si>
@@ -413,308 +422,299 @@
     <t>SECRIERU.NATALIA</t>
   </si>
   <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>DE LUCA ALESSIA</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>FELICIA.FALCONIO</t>
   </si>
   <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>DE LUCA ALESSIA</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
     <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - (NON PULITISSIMA)</t>
-  </si>
-  <si>
-    <t>HC431JD</t>
-  </si>
-  <si>
-    <t>HC634JD</t>
-  </si>
-  <si>
-    <t>HC713JD</t>
-  </si>
-  <si>
-    <t>HC393JD</t>
-  </si>
-  <si>
-    <t>HC599JE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,25 +748,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -804,7 +796,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -838,7 +830,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -873,10 +864,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1049,14 +1039,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1073,1184 +1060,1196 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C6" s="1">
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E14" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E15" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E17" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E20" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E21" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E25" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E29" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E31" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="C34" t="s">
+        <v>188</v>
       </c>
       <c r="E34" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E36" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C38" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E38" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E39" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E41" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E42" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E43" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C44" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E44" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C45" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E45" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E46" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>135</v>
+      </c>
+      <c r="C47" t="s">
+        <v>188</v>
       </c>
       <c r="E47" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E48" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E49" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E50" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E51" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E54" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E55" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E56" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C57" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E57" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E58" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E60" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E61" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E62" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E63" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E64" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C65" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E65" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E66" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E67" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C68" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E68" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E69" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E70" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C71" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E71" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E72" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E73" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E74" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E75" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C76" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E76" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E77" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E78" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E79" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C80" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E80" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C81" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E81" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C82" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D82" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E82" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E83" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>184</v>
+      </c>
+      <c r="C84" t="s">
+        <v>188</v>
       </c>
       <c r="D84" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>185</v>
+      </c>
+      <c r="C85" t="s">
+        <v>188</v>
       </c>
       <c r="D85" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D86" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D87" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D88" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D90" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D91" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D92" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D93" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D94" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>223</v>
+        <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D95" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>224</v>
+        <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D96" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D97" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D98" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>227</v>
+        <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D99" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2259,50 +2258,78 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="229">
   <si>
     <t>targa</t>
   </si>
@@ -326,385 +326,382 @@
     <t>HC599JE</t>
   </si>
   <si>
+    <t>IANNONE SAMANTHA</t>
+  </si>
+  <si>
+    <t>CENTRO DAMA - DA PORTARE DA PASQUARELLI</t>
+  </si>
+  <si>
+    <t>D'ORAZIO CINZIA</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
+  </si>
+  <si>
+    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
+  </si>
+  <si>
+    <t>VOCIONE MICHELA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>DE LUCA ALESSIA</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>CENTRO DAMA - DA PORTARE DA PASQUARELLI</t>
-  </si>
-  <si>
-    <t>D'ORAZIO CINZIA</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
-  </si>
-  <si>
-    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
-  </si>
-  <si>
-    <t>VOCIONE MICHELA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>DE LUCA ALESSIA</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
   </si>
 </sst>
 </file>
@@ -2259,7 +2256,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2278,58 +2275,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>228</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_6386111469A35802FECF53642D96CF9E2BED84FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E429F1C4-2B47-4E19-B899-705FDFFEE476}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="231">
   <si>
     <t>targa</t>
   </si>
@@ -383,335 +389,341 @@
     <t>BONFITTO DAVIDE</t>
   </si>
   <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA AL RITIRO 25-09-26</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>DE LUCA ALESSIA</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
     <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>DE LUCA ALESSIA</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,17 +757,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -793,7 +813,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -827,6 +847,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -861,9 +882,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1036,11 +1058,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1057,7 +1084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1068,10 +1095,10 @@
         <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1082,10 +1109,10 @@
         <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1096,10 +1123,10 @@
         <v>189</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1107,10 +1134,10 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1121,10 +1148,10 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1135,10 +1162,10 @@
         <v>190</v>
       </c>
       <c r="E7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1146,10 +1173,10 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1157,10 +1184,10 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1171,10 +1198,10 @@
         <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1182,10 +1209,10 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1193,10 +1220,10 @@
         <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1207,10 +1234,10 @@
         <v>192</v>
       </c>
       <c r="E13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1221,10 +1248,10 @@
         <v>193</v>
       </c>
       <c r="E14" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1235,10 +1262,10 @@
         <v>193</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1246,10 +1273,10 @@
         <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1260,10 +1287,10 @@
         <v>194</v>
       </c>
       <c r="E17" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1274,10 +1301,10 @@
         <v>193</v>
       </c>
       <c r="E18" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1288,10 +1315,10 @@
         <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1302,10 +1329,10 @@
         <v>196</v>
       </c>
       <c r="E20" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1313,13 +1340,13 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E21" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1327,926 +1354,959 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="C23" t="s">
+        <v>187</v>
       </c>
       <c r="E23" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="C24" t="s">
+        <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E25" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
         <v>195</v>
       </c>
       <c r="E28" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E29" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>187</v>
       </c>
       <c r="E30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
         <v>188</v>
       </c>
       <c r="E34" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E38" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E41" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E44" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
         <v>188</v>
       </c>
       <c r="E45" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E46" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C47" t="s">
         <v>188</v>
       </c>
       <c r="E47" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E51" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E52" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C53" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E54" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E55" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E56" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E57" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E58" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E59" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E60" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E61" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E62" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E63" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E64" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E65" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E66" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E67" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E68" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E69" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E70" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E71" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E72" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E73" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E74" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E75" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E76" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E78" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E79" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C80" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E80" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C81" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E81" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C82" t="s">
+        <v>210</v>
+      </c>
+      <c r="D82" t="s">
         <v>211</v>
       </c>
-      <c r="D82" t="s">
-        <v>212</v>
-      </c>
       <c r="E82" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
+        <v>210</v>
+      </c>
+      <c r="D83" t="s">
         <v>211</v>
       </c>
-      <c r="D83" t="s">
-        <v>212</v>
-      </c>
       <c r="E83" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C84" t="s">
         <v>188</v>
       </c>
       <c r="D84" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>212</v>
+      </c>
+      <c r="E84" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C85" t="s">
         <v>188</v>
       </c>
       <c r="D85" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>212</v>
+      </c>
+      <c r="E85" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D86" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D87" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D89" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D90" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D91" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>184</v>
+      </c>
+      <c r="C92" t="s">
+        <v>187</v>
       </c>
       <c r="D92" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>212</v>
+      </c>
+      <c r="E92" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D93" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>185</v>
+      </c>
+      <c r="C94" t="s">
+        <v>187</v>
       </c>
       <c r="D94" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>212</v>
+      </c>
+      <c r="E94" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D95" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D96" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
         <v>186</v>
       </c>
+      <c r="C97" t="s">
+        <v>187</v>
+      </c>
       <c r="D97" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E97" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D98" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D99" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2255,35 +2315,119 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" t="s">
         <v>224</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>225</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>226</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>228</v>
       </c>
-      <c r="C2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
         <v>187</v>
       </c>
     </row>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_6386111469A35802FECF53642D96CF9E2BED84FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E429F1C4-2B47-4E19-B899-705FDFFEE476}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="230">
   <si>
     <t>targa</t>
   </si>
@@ -446,284 +440,281 @@
     <t>DE LUCA ALESSIA</t>
   </si>
   <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>KLODIAN ALIAJ</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,25 +748,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -813,7 +796,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -847,7 +830,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -882,10 +864,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1058,16 +1039,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1084,7 +1060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1092,13 +1068,13 @@
         <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1106,13 +1082,13 @@
         <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1120,13 +1096,13 @@
         <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1134,10 +1110,10 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1148,10 +1124,10 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1159,13 +1135,13 @@
         <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1173,10 +1149,10 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1184,10 +1160,10 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1195,13 +1171,13 @@
         <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1209,10 +1185,10 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1220,10 +1196,10 @@
         <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1231,13 +1207,13 @@
         <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E13" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1245,13 +1221,13 @@
         <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E14" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1259,13 +1235,13 @@
         <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1273,10 +1249,10 @@
         <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1284,13 +1260,13 @@
         <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1298,13 +1274,13 @@
         <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1312,13 +1288,13 @@
         <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1326,13 +1302,13 @@
         <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E20" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1340,13 +1316,13 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1354,10 +1330,10 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1365,13 +1341,13 @@
         <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E23" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1379,13 +1355,13 @@
         <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1393,13 +1369,13 @@
         <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E25" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1407,10 +1383,10 @@
         <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1418,10 +1394,10 @@
         <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1429,13 +1405,13 @@
         <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E28" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1443,13 +1419,13 @@
         <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E29" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1457,13 +1433,13 @@
         <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1471,10 +1447,10 @@
         <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1482,10 +1458,10 @@
         <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1493,10 +1469,10 @@
         <v>132</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1504,13 +1480,13 @@
         <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E34" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1518,10 +1494,10 @@
         <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1529,10 +1505,10 @@
         <v>134</v>
       </c>
       <c r="E36" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1540,10 +1516,10 @@
         <v>135</v>
       </c>
       <c r="E37" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1551,13 +1527,13 @@
         <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E38" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1565,10 +1541,10 @@
         <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1576,10 +1552,10 @@
         <v>138</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1587,10 +1563,10 @@
         <v>139</v>
       </c>
       <c r="E41" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1598,63 +1574,66 @@
         <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E42" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>122</v>
+      </c>
+      <c r="C43" t="s">
+        <v>202</v>
       </c>
       <c r="E43" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E46" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1662,651 +1641,660 @@
         <v>122</v>
       </c>
       <c r="C47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E47" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E52" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C53" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E54" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E55" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E56" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E57" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E58" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E60" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E62" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E63" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E64" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E65" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E66" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E67" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E68" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E69" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E70" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E71" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E72" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E73" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E74" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E75" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E76" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E77" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E78" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E80" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C81" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E81" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D82" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E82" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D83" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E83" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C84" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D84" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E84" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E85" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D86" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D87" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D88" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="C89" t="s">
+        <v>202</v>
       </c>
       <c r="D89" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
         <v>183</v>
       </c>
+      <c r="C90" t="s">
+        <v>202</v>
+      </c>
       <c r="D90" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>183</v>
+        <v>184</v>
+      </c>
+      <c r="C91" t="s">
+        <v>202</v>
       </c>
       <c r="D91" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D92" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E92" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D93" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D94" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E94" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D95" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D96" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C97" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D97" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E97" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D98" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D99" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2315,55 +2303,55 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
         <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>229</v>
@@ -2372,63 +2360,35 @@
         <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
         <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_5CA5176C2C602D447FE3B5F49D25C59C9C5C70D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF12865-09E3-4FA4-B8E0-0CCE999FE0A2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="231">
   <si>
     <t>targa</t>
   </si>
@@ -563,158 +569,161 @@
     <t>DA ASSEGNARE - MINICUCCI</t>
   </si>
   <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>KLODIAN ALIAJ</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,17 +757,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -796,7 +813,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -830,6 +847,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -864,9 +882,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1039,11 +1058,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1071,10 +1095,10 @@
         <v>188</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1085,10 +1109,10 @@
         <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1099,10 +1123,10 @@
         <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1110,10 +1134,10 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1124,10 +1148,10 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1138,10 +1162,10 @@
         <v>191</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1149,10 +1173,10 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1160,10 +1184,10 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1174,10 +1198,10 @@
         <v>192</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1185,10 +1209,10 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1196,10 +1220,10 @@
         <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1210,10 +1234,10 @@
         <v>193</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1224,10 +1248,10 @@
         <v>194</v>
       </c>
       <c r="E14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1238,10 +1262,10 @@
         <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1249,10 +1273,10 @@
         <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1263,10 +1287,10 @@
         <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1277,10 +1301,10 @@
         <v>194</v>
       </c>
       <c r="E18" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1291,10 +1315,10 @@
         <v>196</v>
       </c>
       <c r="E19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1305,10 +1329,10 @@
         <v>197</v>
       </c>
       <c r="E20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1319,10 +1343,10 @@
         <v>188</v>
       </c>
       <c r="E21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1330,10 +1354,10 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1344,10 +1368,10 @@
         <v>188</v>
       </c>
       <c r="E23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1358,10 +1382,10 @@
         <v>188</v>
       </c>
       <c r="E24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1372,10 +1396,10 @@
         <v>198</v>
       </c>
       <c r="E25" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1383,10 +1407,10 @@
         <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1394,10 +1418,10 @@
         <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1408,10 +1432,10 @@
         <v>196</v>
       </c>
       <c r="E28" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1422,10 +1446,10 @@
         <v>199</v>
       </c>
       <c r="E29" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1436,10 +1460,10 @@
         <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1447,10 +1471,10 @@
         <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1458,10 +1482,10 @@
         <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1469,10 +1493,10 @@
         <v>132</v>
       </c>
       <c r="E33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1483,10 +1507,10 @@
         <v>189</v>
       </c>
       <c r="E34" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1494,10 +1518,10 @@
         <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1505,10 +1529,10 @@
         <v>134</v>
       </c>
       <c r="E36" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1516,10 +1540,10 @@
         <v>135</v>
       </c>
       <c r="E37" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1530,10 +1554,10 @@
         <v>200</v>
       </c>
       <c r="E38" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1541,10 +1565,10 @@
         <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1552,10 +1576,10 @@
         <v>138</v>
       </c>
       <c r="E40" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1563,10 +1587,10 @@
         <v>139</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1577,10 +1601,10 @@
         <v>201</v>
       </c>
       <c r="E42" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1591,10 +1615,10 @@
         <v>202</v>
       </c>
       <c r="E43" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1605,10 +1629,10 @@
         <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1619,10 +1643,10 @@
         <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1630,10 +1654,10 @@
         <v>143</v>
       </c>
       <c r="E46" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1644,10 +1668,10 @@
         <v>189</v>
       </c>
       <c r="E47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -1655,10 +1679,10 @@
         <v>144</v>
       </c>
       <c r="E48" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1666,10 +1690,10 @@
         <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1677,10 +1701,10 @@
         <v>146</v>
       </c>
       <c r="E50" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -1688,10 +1712,10 @@
         <v>147</v>
       </c>
       <c r="E51" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1699,10 +1723,10 @@
         <v>148</v>
       </c>
       <c r="E52" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -1712,8 +1736,11 @@
       <c r="C53" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="E53" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -1721,10 +1748,10 @@
         <v>150</v>
       </c>
       <c r="E54" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -1732,10 +1759,10 @@
         <v>151</v>
       </c>
       <c r="E55" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -1743,10 +1770,10 @@
         <v>152</v>
       </c>
       <c r="E56" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -1757,10 +1784,10 @@
         <v>202</v>
       </c>
       <c r="E57" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -1768,10 +1795,10 @@
         <v>153</v>
       </c>
       <c r="E58" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -1779,10 +1806,10 @@
         <v>154</v>
       </c>
       <c r="E59" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -1790,10 +1817,10 @@
         <v>155</v>
       </c>
       <c r="E60" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -1801,10 +1828,10 @@
         <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -1812,10 +1839,10 @@
         <v>157</v>
       </c>
       <c r="E62" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -1823,10 +1850,10 @@
         <v>158</v>
       </c>
       <c r="E63" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -1837,10 +1864,10 @@
         <v>205</v>
       </c>
       <c r="E64" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1851,10 +1878,10 @@
         <v>206</v>
       </c>
       <c r="E65" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -1862,10 +1889,10 @@
         <v>161</v>
       </c>
       <c r="E66" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -1873,10 +1900,10 @@
         <v>162</v>
       </c>
       <c r="E67" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -1887,10 +1914,10 @@
         <v>207</v>
       </c>
       <c r="E68" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -1898,10 +1925,10 @@
         <v>164</v>
       </c>
       <c r="E69" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1909,10 +1936,10 @@
         <v>165</v>
       </c>
       <c r="E70" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -1923,10 +1950,10 @@
         <v>208</v>
       </c>
       <c r="E71" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -1934,10 +1961,10 @@
         <v>167</v>
       </c>
       <c r="E72" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -1945,10 +1972,10 @@
         <v>168</v>
       </c>
       <c r="E73" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -1959,10 +1986,10 @@
         <v>209</v>
       </c>
       <c r="E74" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -1970,10 +1997,10 @@
         <v>170</v>
       </c>
       <c r="E75" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -1984,10 +2011,10 @@
         <v>210</v>
       </c>
       <c r="E76" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -1995,10 +2022,10 @@
         <v>172</v>
       </c>
       <c r="E77" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -2006,10 +2033,10 @@
         <v>173</v>
       </c>
       <c r="E78" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -2017,10 +2044,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2031,10 +2058,10 @@
         <v>200</v>
       </c>
       <c r="E80" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -2045,10 +2072,10 @@
         <v>211</v>
       </c>
       <c r="E81" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -2059,13 +2086,13 @@
         <v>212</v>
       </c>
       <c r="D82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E82" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -2076,13 +2103,13 @@
         <v>212</v>
       </c>
       <c r="D83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -2093,13 +2120,13 @@
         <v>189</v>
       </c>
       <c r="D84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E84" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -2110,13 +2137,13 @@
         <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E85" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -2124,10 +2151,10 @@
         <v>181</v>
       </c>
       <c r="D86" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -2135,10 +2162,10 @@
         <v>181</v>
       </c>
       <c r="D87" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -2146,10 +2173,10 @@
         <v>181</v>
       </c>
       <c r="D88" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2157,13 +2184,16 @@
         <v>182</v>
       </c>
       <c r="C89" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D89" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>215</v>
+      </c>
+      <c r="E89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -2174,10 +2204,13 @@
         <v>202</v>
       </c>
       <c r="D90" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>215</v>
+      </c>
+      <c r="E90" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -2188,10 +2221,13 @@
         <v>202</v>
       </c>
       <c r="D91" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>215</v>
+      </c>
+      <c r="E91" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -2202,13 +2238,13 @@
         <v>188</v>
       </c>
       <c r="D92" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E92" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -2216,10 +2252,10 @@
         <v>181</v>
       </c>
       <c r="D93" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -2230,13 +2266,13 @@
         <v>188</v>
       </c>
       <c r="D94" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E94" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -2244,10 +2280,10 @@
         <v>181</v>
       </c>
       <c r="D95" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -2255,10 +2291,10 @@
         <v>181</v>
       </c>
       <c r="D96" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -2269,13 +2305,13 @@
         <v>188</v>
       </c>
       <c r="D97" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E97" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -2283,10 +2319,10 @@
         <v>181</v>
       </c>
       <c r="D98" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -2294,7 +2330,7 @@
         <v>181</v>
       </c>
       <c r="D99" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2303,92 +2339,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_5CA5176C2C602D447FE3B5F49D25C59C9C5C70D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF12865-09E3-4FA4-B8E0-0CCE999FE0A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="231">
   <si>
     <t>targa</t>
   </si>
@@ -362,368 +356,368 @@
     <t>SIMONA.PETRAGNANO</t>
   </si>
   <si>
+    <t>DE LUCA ALESSIA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
+  </si>
+  <si>
+    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
+  </si>
+  <si>
+    <t>VOCIONE MICHELA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA AL RITIRO 25-09-26</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>CAVUOTO CHIARA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
-  </si>
-  <si>
-    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
-  </si>
-  <si>
-    <t>VOCIONE MICHELA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA AL RITIRO 25-09-26</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>DE LUCA ALESSIA</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>KLODIAN ALIAJ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,25 +751,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -813,7 +799,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -847,7 +833,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -882,10 +867,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1058,16 +1042,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1084,7 +1063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1098,7 +1077,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1112,7 +1091,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1126,7 +1105,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1137,7 +1116,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1151,7 +1130,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1165,7 +1144,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1176,7 +1155,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1187,7 +1166,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1201,7 +1180,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1212,18 +1191,21 @@
         <v>217</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>113</v>
       </c>
+      <c r="C12" t="s">
+        <v>193</v>
+      </c>
       <c r="E12" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1231,13 +1213,13 @@
         <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E13" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1245,13 +1227,13 @@
         <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1259,13 +1241,13 @@
         <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1276,7 +1258,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1284,13 +1266,13 @@
         <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E17" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1298,13 +1280,13 @@
         <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1312,13 +1294,13 @@
         <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E19" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1326,13 +1308,13 @@
         <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E20" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1346,7 +1328,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1357,7 +1339,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1371,7 +1353,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1385,7 +1367,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1393,13 +1375,13 @@
         <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E25" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1410,7 +1392,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1421,7 +1403,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1429,13 +1411,13 @@
         <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1443,13 +1425,13 @@
         <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E29" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1463,7 +1445,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1474,7 +1456,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1485,7 +1467,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1496,7 +1478,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1510,7 +1492,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1521,7 +1503,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1532,7 +1514,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1543,7 +1525,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1551,13 +1533,13 @@
         <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1568,7 +1550,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1579,7 +1561,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1590,21 +1572,21 @@
         <v>223</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E42" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1618,12 +1600,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
         <v>203</v>
@@ -1632,12 +1614,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
         <v>189</v>
@@ -1646,18 +1628,18 @@
         <v>216</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1671,67 +1653,67 @@
         <v>218</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E49" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
         <v>204</v>
@@ -1740,40 +1722,40 @@
         <v>220</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E54" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E55" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E56" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -1787,78 +1769,78 @@
         <v>217</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E58" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E59" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E61" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E62" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E63" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C64" t="s">
         <v>205</v>
@@ -1867,12 +1849,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C65" t="s">
         <v>206</v>
@@ -1881,34 +1863,34 @@
         <v>218</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E67" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" t="s">
         <v>207</v>
@@ -1917,34 +1899,34 @@
         <v>217</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E69" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E70" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
         <v>208</v>
@@ -1953,34 +1935,34 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E72" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C74" t="s">
         <v>209</v>
@@ -1989,23 +1971,23 @@
         <v>219</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E75" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
         <v>210</v>
@@ -2014,59 +1996,59 @@
         <v>220</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E77" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E78" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E79" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C80" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E80" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s">
         <v>211</v>
@@ -2075,12 +2057,12 @@
         <v>222</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
         <v>212</v>
@@ -2092,12 +2074,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C83" t="s">
         <v>212</v>
@@ -2109,12 +2091,12 @@
         <v>222</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C84" t="s">
         <v>189</v>
@@ -2126,12 +2108,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C85" t="s">
         <v>189</v>
@@ -2143,18 +2125,21 @@
         <v>218</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="C86" t="s">
+        <v>193</v>
       </c>
       <c r="D86" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -2165,7 +2150,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -2176,7 +2161,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2193,7 +2178,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -2210,7 +2195,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -2227,7 +2212,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -2244,7 +2229,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -2255,7 +2240,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -2272,7 +2257,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -2283,7 +2268,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -2294,7 +2279,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -2311,7 +2296,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -2322,12 +2307,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>181</v>
+        <v>162</v>
+      </c>
+      <c r="C99" t="s">
+        <v>193</v>
       </c>
       <c r="D99" t="s">
         <v>215</v>
@@ -2339,11 +2327,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>226</v>
       </c>
@@ -2357,18 +2345,60 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>230</v>
       </c>
-      <c r="C2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D2" t="s">
-        <v>213</v>
+      <c r="C4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="233">
   <si>
     <t>targa</t>
   </si>
@@ -413,301 +413,307 @@
     <t>NATHALIE.BOVE</t>
   </si>
   <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>CAVUOTO CHIARA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>SECRIERU NATALIE</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>COTOLLESSA FRANCESCA</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>PARDI ELIANA</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
     <t>SECRIERU.NATALIA</t>
   </si>
   <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
     <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>CAVUOTO CHIARA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
   </si>
 </sst>
 </file>
@@ -1472,7 +1478,10 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>122</v>
+      </c>
+      <c r="C33" t="s">
+        <v>201</v>
       </c>
       <c r="E33" t="s">
         <v>217</v>
@@ -1497,7 +1506,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
         <v>222</v>
@@ -1508,7 +1517,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
         <v>223</v>
@@ -1519,7 +1528,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
         <v>217</v>
@@ -1530,10 +1539,10 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -1544,7 +1553,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E39" t="s">
         <v>223</v>
@@ -1555,7 +1564,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
         <v>220</v>
@@ -1566,7 +1575,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E41" t="s">
         <v>223</v>
@@ -1594,7 +1603,7 @@
         <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
         <v>225</v>
@@ -1605,10 +1614,10 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E44" t="s">
         <v>224</v>
@@ -1619,7 +1628,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
         <v>189</v>
@@ -1633,7 +1642,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
         <v>223</v>
@@ -1658,7 +1667,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
         <v>220</v>
@@ -1669,7 +1678,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s">
         <v>218</v>
@@ -1680,7 +1689,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E50" t="s">
         <v>225</v>
@@ -1691,7 +1700,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
         <v>220</v>
@@ -1702,7 +1711,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s">
         <v>218</v>
@@ -1713,10 +1722,10 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E53" t="s">
         <v>220</v>
@@ -1727,7 +1736,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E54" t="s">
         <v>224</v>
@@ -1738,7 +1747,10 @@
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>122</v>
+      </c>
+      <c r="C55" t="s">
+        <v>201</v>
       </c>
       <c r="E55" t="s">
         <v>217</v>
@@ -1749,7 +1761,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E56" t="s">
         <v>222</v>
@@ -1763,7 +1775,7 @@
         <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E57" t="s">
         <v>217</v>
@@ -1774,7 +1786,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E58" t="s">
         <v>223</v>
@@ -1785,7 +1797,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E59" t="s">
         <v>220</v>
@@ -1796,7 +1808,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E60" t="s">
         <v>217</v>
@@ -1807,7 +1819,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E61" t="s">
         <v>220</v>
@@ -1818,7 +1830,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E62" t="s">
         <v>218</v>
@@ -1829,7 +1841,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E63" t="s">
         <v>220</v>
@@ -1840,10 +1852,10 @@
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E64" t="s">
         <v>220</v>
@@ -1854,10 +1866,10 @@
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="C65" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E65" t="s">
         <v>218</v>
@@ -1868,7 +1880,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E66" t="s">
         <v>217</v>
@@ -1879,7 +1891,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E67" t="s">
         <v>222</v>
@@ -1890,7 +1902,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
         <v>207</v>
@@ -1904,7 +1916,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>223</v>
@@ -1915,7 +1927,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E70" t="s">
         <v>218</v>
@@ -1926,7 +1938,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C71" t="s">
         <v>208</v>
@@ -1940,7 +1952,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E72" t="s">
         <v>220</v>
@@ -1951,7 +1963,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -1962,7 +1974,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C74" t="s">
         <v>209</v>
@@ -1976,7 +1988,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E75" t="s">
         <v>223</v>
@@ -1987,7 +1999,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C76" t="s">
         <v>210</v>
@@ -2001,7 +2013,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E77" t="s">
         <v>218</v>
@@ -2012,7 +2024,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E78" t="s">
         <v>218</v>
@@ -2023,7 +2035,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E79" t="s">
         <v>218</v>
@@ -2034,10 +2046,10 @@
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C80" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E80" t="s">
         <v>218</v>
@@ -2048,7 +2060,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C81" t="s">
         <v>211</v>
@@ -2062,7 +2074,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C82" t="s">
         <v>212</v>
@@ -2079,7 +2091,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C83" t="s">
         <v>212</v>
@@ -2096,7 +2108,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C84" t="s">
         <v>189</v>
@@ -2113,7 +2125,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C85" t="s">
         <v>189</v>
@@ -2130,7 +2142,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C86" t="s">
         <v>193</v>
@@ -2144,7 +2156,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D87" t="s">
         <v>215</v>
@@ -2155,7 +2167,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D88" t="s">
         <v>215</v>
@@ -2166,7 +2178,7 @@
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C89" t="s">
         <v>213</v>
@@ -2183,10 +2195,10 @@
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D90" t="s">
         <v>215</v>
@@ -2200,10 +2212,10 @@
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C91" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D91" t="s">
         <v>215</v>
@@ -2217,7 +2229,7 @@
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C92" t="s">
         <v>188</v>
@@ -2234,7 +2246,10 @@
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>181</v>
+        <v>183</v>
+      </c>
+      <c r="C93" t="s">
+        <v>201</v>
       </c>
       <c r="D93" t="s">
         <v>215</v>
@@ -2245,7 +2260,7 @@
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C94" t="s">
         <v>188</v>
@@ -2262,7 +2277,7 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D95" t="s">
         <v>215</v>
@@ -2273,7 +2288,10 @@
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>181</v>
+        <v>185</v>
+      </c>
+      <c r="C96" t="s">
+        <v>201</v>
       </c>
       <c r="D96" t="s">
         <v>215</v>
@@ -2284,7 +2302,7 @@
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C97" t="s">
         <v>188</v>
@@ -2301,7 +2319,10 @@
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>181</v>
+        <v>187</v>
+      </c>
+      <c r="C98" t="s">
+        <v>201</v>
       </c>
       <c r="D98" t="s">
         <v>215</v>
@@ -2312,7 +2333,7 @@
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C99" t="s">
         <v>193</v>
@@ -2328,7 +2349,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2347,58 +2368,86 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>230</v>
       </c>
       <c r="C5" t="s">
         <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_17D2F1106943585B763FC92919CE25983137B28D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F7AD129-DB70-436C-A601-D63DFD8821DD}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="233">
   <si>
     <t>targa</t>
   </si>
@@ -638,9 +644,6 @@
     <t>2026-03-09</t>
   </si>
   <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
     <t>2026-06-29</t>
   </si>
   <si>
@@ -714,16 +717,19 @@
   </si>
   <si>
     <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>CAMISCIA MONIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -752,22 +758,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -805,7 +820,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -839,6 +854,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -873,9 +889,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1048,11 +1065,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1069,7 +1090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1080,10 +1101,10 @@
         <v>188</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1094,10 +1115,10 @@
         <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1108,10 +1129,10 @@
         <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1119,10 +1140,10 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1133,10 +1154,10 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1147,10 +1168,10 @@
         <v>191</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1158,10 +1179,10 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1169,10 +1190,10 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1183,10 +1204,10 @@
         <v>192</v>
       </c>
       <c r="E10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1194,10 +1215,10 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1208,10 +1229,10 @@
         <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1222,10 +1243,10 @@
         <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1236,10 +1257,10 @@
         <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1250,10 +1271,10 @@
         <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1261,10 +1282,10 @@
         <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1275,10 +1296,10 @@
         <v>196</v>
       </c>
       <c r="E17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1289,10 +1310,10 @@
         <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1303,10 +1324,10 @@
         <v>197</v>
       </c>
       <c r="E19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1317,10 +1338,10 @@
         <v>198</v>
       </c>
       <c r="E20" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1331,10 +1352,10 @@
         <v>188</v>
       </c>
       <c r="E21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1342,10 +1363,10 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1356,10 +1377,10 @@
         <v>188</v>
       </c>
       <c r="E23" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1370,10 +1391,10 @@
         <v>188</v>
       </c>
       <c r="E24" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1384,10 +1405,10 @@
         <v>199</v>
       </c>
       <c r="E25" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1395,10 +1416,10 @@
         <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1406,10 +1427,10 @@
         <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1420,10 +1441,10 @@
         <v>197</v>
       </c>
       <c r="E28" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1434,10 +1455,10 @@
         <v>200</v>
       </c>
       <c r="E29" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1448,10 +1469,10 @@
         <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1459,10 +1480,10 @@
         <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1470,10 +1491,10 @@
         <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1484,10 +1505,10 @@
         <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1498,10 +1519,10 @@
         <v>189</v>
       </c>
       <c r="E34" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1509,10 +1530,10 @@
         <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1520,10 +1541,10 @@
         <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1531,10 +1552,10 @@
         <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1545,10 +1566,10 @@
         <v>202</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1556,10 +1577,10 @@
         <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1567,10 +1588,10 @@
         <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1578,10 +1599,10 @@
         <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1592,10 +1613,10 @@
         <v>193</v>
       </c>
       <c r="E42" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1606,10 +1627,10 @@
         <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1620,10 +1641,10 @@
         <v>204</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1634,10 +1655,10 @@
         <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1645,10 +1666,10 @@
         <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1659,10 +1680,10 @@
         <v>189</v>
       </c>
       <c r="E47" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -1670,10 +1691,10 @@
         <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1681,10 +1702,10 @@
         <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1692,10 +1713,10 @@
         <v>144</v>
       </c>
       <c r="E50" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -1703,10 +1724,10 @@
         <v>145</v>
       </c>
       <c r="E51" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1714,10 +1735,10 @@
         <v>146</v>
       </c>
       <c r="E52" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -1728,10 +1749,10 @@
         <v>205</v>
       </c>
       <c r="E53" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -1739,10 +1760,10 @@
         <v>148</v>
       </c>
       <c r="E54" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -1753,10 +1774,10 @@
         <v>201</v>
       </c>
       <c r="E55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -1764,10 +1785,10 @@
         <v>149</v>
       </c>
       <c r="E56" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -1778,10 +1799,10 @@
         <v>203</v>
       </c>
       <c r="E57" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -1789,10 +1810,10 @@
         <v>150</v>
       </c>
       <c r="E58" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -1800,10 +1821,10 @@
         <v>151</v>
       </c>
       <c r="E59" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -1811,10 +1832,10 @@
         <v>152</v>
       </c>
       <c r="E60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -1822,10 +1843,10 @@
         <v>153</v>
       </c>
       <c r="E61" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -1833,10 +1854,10 @@
         <v>154</v>
       </c>
       <c r="E62" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -1844,10 +1865,10 @@
         <v>155</v>
       </c>
       <c r="E63" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -1858,10 +1879,10 @@
         <v>206</v>
       </c>
       <c r="E64" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1872,10 +1893,10 @@
         <v>201</v>
       </c>
       <c r="E65" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -1883,10 +1904,10 @@
         <v>157</v>
       </c>
       <c r="E66" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -1894,24 +1915,24 @@
         <v>158</v>
       </c>
       <c r="E67" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>159</v>
-      </c>
-      <c r="C68" t="s">
-        <v>207</v>
+        <v>232</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46300</v>
       </c>
       <c r="E68" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -1919,10 +1940,10 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1930,10 +1951,10 @@
         <v>161</v>
       </c>
       <c r="E70" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -1941,13 +1962,13 @@
         <v>162</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E71" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -1955,10 +1976,10 @@
         <v>163</v>
       </c>
       <c r="E72" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -1966,10 +1987,10 @@
         <v>164</v>
       </c>
       <c r="E73" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -1977,13 +1998,13 @@
         <v>165</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E74" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -1991,10 +2012,10 @@
         <v>166</v>
       </c>
       <c r="E75" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -2002,13 +2023,13 @@
         <v>167</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E76" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -2016,10 +2037,10 @@
         <v>168</v>
       </c>
       <c r="E77" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -2027,10 +2048,10 @@
         <v>169</v>
       </c>
       <c r="E78" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -2038,10 +2059,10 @@
         <v>170</v>
       </c>
       <c r="E79" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2052,10 +2073,10 @@
         <v>202</v>
       </c>
       <c r="E80" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -2063,13 +2084,13 @@
         <v>172</v>
       </c>
       <c r="C81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -2077,16 +2098,16 @@
         <v>173</v>
       </c>
       <c r="C82" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D82" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E82" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -2094,16 +2115,16 @@
         <v>174</v>
       </c>
       <c r="C83" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D83" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E83" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -2114,13 +2135,13 @@
         <v>189</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -2131,13 +2152,13 @@
         <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E85" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -2148,10 +2169,13 @@
         <v>193</v>
       </c>
       <c r="D86" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>214</v>
+      </c>
+      <c r="E86" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -2159,10 +2183,10 @@
         <v>178</v>
       </c>
       <c r="D87" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -2170,10 +2194,10 @@
         <v>178</v>
       </c>
       <c r="D88" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2181,16 +2205,16 @@
         <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -2201,13 +2225,13 @@
         <v>203</v>
       </c>
       <c r="D90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -2218,13 +2242,13 @@
         <v>203</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -2235,13 +2259,13 @@
         <v>188</v>
       </c>
       <c r="D92" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E92" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -2252,10 +2276,13 @@
         <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>214</v>
+      </c>
+      <c r="E93" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -2266,13 +2293,13 @@
         <v>188</v>
       </c>
       <c r="D94" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E94" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -2280,10 +2307,10 @@
         <v>178</v>
       </c>
       <c r="D95" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -2294,10 +2321,13 @@
         <v>201</v>
       </c>
       <c r="D96" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>214</v>
+      </c>
+      <c r="E96" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -2308,13 +2338,13 @@
         <v>188</v>
       </c>
       <c r="D97" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E97" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -2325,10 +2355,13 @@
         <v>201</v>
       </c>
       <c r="D98" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>214</v>
+      </c>
+      <c r="E98" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -2339,7 +2372,10 @@
         <v>193</v>
       </c>
       <c r="D99" t="s">
-        <v>215</v>
+        <v>214</v>
+      </c>
+      <c r="E99" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -2348,25 +2384,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" t="s">
         <v>226</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>227</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>228</v>
       </c>
-      <c r="D1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -2380,7 +2416,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2394,7 +2430,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>101</v>
       </c>
@@ -2408,12 +2444,12 @@
         <v>201</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" t="s">
         <v>122</v>
@@ -2422,12 +2458,12 @@
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C6" t="s">
         <v>122</v>
@@ -2436,12 +2472,12 @@
         <v>201</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7" t="s">
         <v>122</v>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_17D2F1106943585B763FC92919CE25983137B28D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F7AD129-DB70-436C-A601-D63DFD8821DD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="232">
   <si>
     <t>targa</t>
   </si>
@@ -335,401 +329,398 @@
     <t>IANNONE SAMANTHA</t>
   </si>
   <si>
+    <t>IN ASSISTENZA   06-10-26</t>
+  </si>
+  <si>
+    <t>D'ORAZIO CINZIA</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>DE LUCA ALESSIA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
+  </si>
+  <si>
+    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
+  </si>
+  <si>
+    <t>VOCIONE MICHELA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - PRONTA AL RITIRO 25-09-26</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA  (ERA DEL NOD PESCARA)  06-10-26</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>CAMISCIA MONIA</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>CAVUOTO CHIARA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>SECRIERU NATALIE</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>COTOLLESSA FRANCESCA</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>PARDI ELIANA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
     <t>CENTRO DAMA - DA PORTARE DA PASQUARELLI</t>
-  </si>
-  <si>
-    <t>D'ORAZIO CINZIA</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>DE LUCA ALESSIA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
-  </si>
-  <si>
-    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
-  </si>
-  <si>
-    <t>VOCIONE MICHELA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - PRONTA AL RITIRO 25-09-26</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>CAVUOTO CHIARA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>SECRIERU NATALIE</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>COTOLLESSA FRANCESCA</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>PARDI ELIANA</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>CAMISCIA MONIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -758,31 +749,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -820,7 +802,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -854,7 +836,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -889,10 +870,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1065,15 +1045,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1090,7 +1066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1098,13 +1074,13 @@
         <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1112,13 +1088,13 @@
         <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1126,13 +1102,13 @@
         <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1140,10 +1116,10 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1154,10 +1130,10 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1165,13 +1141,13 @@
         <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1179,10 +1155,10 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1190,10 +1166,10 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1201,13 +1177,13 @@
         <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1215,10 +1191,10 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1226,13 +1202,13 @@
         <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1240,13 +1216,13 @@
         <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1254,13 +1230,13 @@
         <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1268,13 +1244,13 @@
         <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1282,10 +1258,10 @@
         <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1293,13 +1269,13 @@
         <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E17" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1307,13 +1283,13 @@
         <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1321,13 +1297,13 @@
         <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1335,13 +1311,13 @@
         <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1349,13 +1325,13 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1363,10 +1339,10 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1374,13 +1350,13 @@
         <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1388,13 +1364,13 @@
         <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1402,13 +1378,13 @@
         <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E25" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1416,10 +1392,10 @@
         <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1427,10 +1403,10 @@
         <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1438,13 +1414,13 @@
         <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E28" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1452,13 +1428,13 @@
         <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E29" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1466,13 +1442,13 @@
         <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E30" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1480,10 +1456,10 @@
         <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1491,10 +1467,10 @@
         <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1502,13 +1478,13 @@
         <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1516,13 +1492,13 @@
         <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1530,10 +1506,10 @@
         <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1541,10 +1517,10 @@
         <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1552,10 +1528,10 @@
         <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1563,13 +1539,13 @@
         <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E38" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1577,10 +1553,10 @@
         <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1588,10 +1564,10 @@
         <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1599,10 +1575,10 @@
         <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1610,13 +1586,13 @@
         <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E42" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1624,13 +1600,13 @@
         <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E43" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1638,13 +1614,13 @@
         <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="E44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1652,13 +1628,13 @@
         <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="E45" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1666,10 +1642,10 @@
         <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1677,13 +1653,13 @@
         <v>122</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="E47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -1691,10 +1667,10 @@
         <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1702,10 +1678,10 @@
         <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1713,10 +1689,10 @@
         <v>144</v>
       </c>
       <c r="E50" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -1724,10 +1700,10 @@
         <v>145</v>
       </c>
       <c r="E51" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1735,10 +1711,10 @@
         <v>146</v>
       </c>
       <c r="E52" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -1746,13 +1722,13 @@
         <v>147</v>
       </c>
       <c r="C53" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E53" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -1760,10 +1736,10 @@
         <v>148</v>
       </c>
       <c r="E54" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -1771,13 +1747,13 @@
         <v>122</v>
       </c>
       <c r="C55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E55" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -1785,10 +1761,10 @@
         <v>149</v>
       </c>
       <c r="E56" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -1796,13 +1772,13 @@
         <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E57" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -1810,10 +1786,10 @@
         <v>150</v>
       </c>
       <c r="E58" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -1821,10 +1797,10 @@
         <v>151</v>
       </c>
       <c r="E59" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -1832,10 +1808,10 @@
         <v>152</v>
       </c>
       <c r="E60" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -1843,10 +1819,10 @@
         <v>153</v>
       </c>
       <c r="E61" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -1854,10 +1830,10 @@
         <v>154</v>
       </c>
       <c r="E62" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -1865,10 +1841,10 @@
         <v>155</v>
       </c>
       <c r="E63" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -1876,13 +1852,13 @@
         <v>156</v>
       </c>
       <c r="C64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E64" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1890,13 +1866,13 @@
         <v>122</v>
       </c>
       <c r="C65" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E65" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -1904,10 +1880,10 @@
         <v>157</v>
       </c>
       <c r="E66" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -1915,24 +1891,24 @@
         <v>158</v>
       </c>
       <c r="E67" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>232</v>
-      </c>
-      <c r="C68" s="2">
+        <v>159</v>
+      </c>
+      <c r="C68" s="1">
         <v>46300</v>
       </c>
       <c r="E68" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -1940,10 +1916,10 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1951,10 +1927,10 @@
         <v>161</v>
       </c>
       <c r="E70" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -1962,13 +1938,13 @@
         <v>162</v>
       </c>
       <c r="C71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E71" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -1976,10 +1952,10 @@
         <v>163</v>
       </c>
       <c r="E72" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -1987,10 +1963,10 @@
         <v>164</v>
       </c>
       <c r="E73" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -1998,13 +1974,13 @@
         <v>165</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E74" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -2012,10 +1988,10 @@
         <v>166</v>
       </c>
       <c r="E75" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -2023,13 +1999,13 @@
         <v>167</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E76" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -2037,10 +2013,10 @@
         <v>168</v>
       </c>
       <c r="E77" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -2048,10 +2024,10 @@
         <v>169</v>
       </c>
       <c r="E78" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -2059,10 +2035,10 @@
         <v>170</v>
       </c>
       <c r="E79" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2070,13 +2046,13 @@
         <v>171</v>
       </c>
       <c r="C80" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E80" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -2084,13 +2060,13 @@
         <v>172</v>
       </c>
       <c r="C81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E81" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -2098,16 +2074,16 @@
         <v>173</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E82" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -2115,16 +2091,16 @@
         <v>174</v>
       </c>
       <c r="C83" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -2132,16 +2108,16 @@
         <v>175</v>
       </c>
       <c r="C84" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E84" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -2149,16 +2125,16 @@
         <v>176</v>
       </c>
       <c r="C85" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D85" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E85" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -2166,16 +2142,16 @@
         <v>177</v>
       </c>
       <c r="C86" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D86" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E86" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -2183,10 +2159,10 @@
         <v>178</v>
       </c>
       <c r="D87" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -2194,10 +2170,10 @@
         <v>178</v>
       </c>
       <c r="D88" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2205,16 +2181,16 @@
         <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E89" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -2222,16 +2198,16 @@
         <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E90" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -2239,16 +2215,16 @@
         <v>181</v>
       </c>
       <c r="C91" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E91" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -2256,16 +2232,16 @@
         <v>182</v>
       </c>
       <c r="C92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D92" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E92" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -2273,16 +2249,16 @@
         <v>183</v>
       </c>
       <c r="C93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D93" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E93" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -2290,16 +2266,16 @@
         <v>184</v>
       </c>
       <c r="C94" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D94" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E94" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -2307,10 +2283,10 @@
         <v>178</v>
       </c>
       <c r="D95" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -2318,16 +2294,16 @@
         <v>185</v>
       </c>
       <c r="C96" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D96" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E96" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -2335,16 +2311,16 @@
         <v>186</v>
       </c>
       <c r="C97" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D97" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E97" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -2352,30 +2328,30 @@
         <v>187</v>
       </c>
       <c r="C98" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D98" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E98" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="C99" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D99" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2384,106 +2360,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="232">
   <si>
     <t>targa</t>
   </si>
@@ -449,268 +449,268 @@
     <t>FRANCESCO.DI.DOMENICANTONIO</t>
   </si>
   <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>CAMISCIA MONIA</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>CAVUOTO CHIARA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>CIMINO NORA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>SECRIERU NATALIE</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>COTOLLESSA FRANCESCA</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>PARDI ELIANA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>CAMISCIA MONIA</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>CAVUOTO CHIARA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>SECRIERU NATALIE</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>COTOLLESSA FRANCESCA</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>PARDI ELIANA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CENTRO DAMA - DA PORTARE DA PASQUARELLI</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1077,7 @@
         <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1091,7 +1091,7 @@
         <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1105,7 +1105,7 @@
         <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1116,7 +1116,7 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1130,7 +1130,7 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1144,7 +1144,7 @@
         <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1155,7 +1155,7 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1166,7 +1166,7 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1180,7 +1180,7 @@
         <v>193</v>
       </c>
       <c r="E10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1191,7 +1191,7 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1205,7 +1205,7 @@
         <v>194</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1219,7 +1219,7 @@
         <v>195</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1233,7 +1233,7 @@
         <v>196</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1247,7 +1247,7 @@
         <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1258,7 +1258,7 @@
         <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1272,7 +1272,7 @@
         <v>197</v>
       </c>
       <c r="E17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1286,7 +1286,7 @@
         <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1300,7 +1300,7 @@
         <v>198</v>
       </c>
       <c r="E19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1314,7 +1314,7 @@
         <v>199</v>
       </c>
       <c r="E20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1328,7 +1328,7 @@
         <v>189</v>
       </c>
       <c r="E21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1339,7 +1339,7 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1353,7 +1353,7 @@
         <v>189</v>
       </c>
       <c r="E23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1367,7 +1367,7 @@
         <v>189</v>
       </c>
       <c r="E24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1381,7 +1381,7 @@
         <v>200</v>
       </c>
       <c r="E25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1392,7 +1392,7 @@
         <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1403,7 +1403,7 @@
         <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1417,7 +1417,7 @@
         <v>198</v>
       </c>
       <c r="E28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1431,7 +1431,7 @@
         <v>201</v>
       </c>
       <c r="E29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1445,7 +1445,7 @@
         <v>189</v>
       </c>
       <c r="E30" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1456,7 +1456,7 @@
         <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1467,7 +1467,7 @@
         <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1481,7 +1481,7 @@
         <v>202</v>
       </c>
       <c r="E33" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1495,7 +1495,7 @@
         <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1506,7 +1506,7 @@
         <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1517,7 +1517,7 @@
         <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1528,7 +1528,7 @@
         <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1542,7 +1542,7 @@
         <v>204</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1553,7 +1553,7 @@
         <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1564,7 +1564,7 @@
         <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1575,7 +1575,7 @@
         <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1589,7 +1589,7 @@
         <v>194</v>
       </c>
       <c r="E42" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1603,7 +1603,7 @@
         <v>205</v>
       </c>
       <c r="E43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1617,7 +1617,7 @@
         <v>190</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1631,7 +1631,7 @@
         <v>203</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1642,7 +1642,7 @@
         <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1656,7 +1656,7 @@
         <v>203</v>
       </c>
       <c r="E47" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1667,7 +1667,7 @@
         <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1678,7 +1678,7 @@
         <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1686,10 +1686,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>122</v>
+      </c>
+      <c r="C50" t="s">
+        <v>206</v>
       </c>
       <c r="E50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1697,10 +1700,10 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1708,10 +1711,10 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1719,13 +1722,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E53" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1733,10 +1736,10 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1750,7 +1753,7 @@
         <v>202</v>
       </c>
       <c r="E55" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1758,10 +1761,10 @@
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1775,7 +1778,7 @@
         <v>205</v>
       </c>
       <c r="E57" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1783,10 +1786,10 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E58" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1794,10 +1797,10 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1805,10 +1808,10 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E60" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1816,10 +1819,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1827,10 +1830,10 @@
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E62" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1838,10 +1841,10 @@
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1849,13 +1852,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E64" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1869,7 +1872,7 @@
         <v>202</v>
       </c>
       <c r="E65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1877,10 +1880,10 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1888,10 +1891,10 @@
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1899,13 +1902,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C68" s="1">
         <v>46300</v>
       </c>
       <c r="E68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1913,10 +1916,10 @@
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1924,10 +1927,10 @@
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1935,13 +1938,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1949,10 +1952,10 @@
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1960,10 +1963,10 @@
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1971,13 +1974,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E74" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1985,10 +1988,10 @@
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1996,13 +1999,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2010,10 +2013,10 @@
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E77" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2021,10 +2024,10 @@
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E78" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2032,10 +2035,10 @@
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E79" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2043,13 +2046,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C80" t="s">
         <v>204</v>
       </c>
       <c r="E80" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2057,13 +2060,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E81" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2071,16 +2074,16 @@
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D82" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E82" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2088,16 +2091,16 @@
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E83" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2105,16 +2108,16 @@
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C84" t="s">
         <v>203</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2122,16 +2125,16 @@
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s">
         <v>203</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E85" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2139,16 +2142,16 @@
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C86" t="s">
         <v>194</v>
       </c>
       <c r="D86" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E86" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2156,10 +2159,10 @@
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D87" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2169,8 +2172,11 @@
       <c r="B88" t="s">
         <v>178</v>
       </c>
+      <c r="C88" t="s">
+        <v>206</v>
+      </c>
       <c r="D88" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2181,13 +2187,13 @@
         <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E89" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2201,10 +2207,10 @@
         <v>205</v>
       </c>
       <c r="D90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E90" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2218,10 +2224,10 @@
         <v>205</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E91" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2235,10 +2241,10 @@
         <v>189</v>
       </c>
       <c r="D92" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2252,10 +2258,10 @@
         <v>202</v>
       </c>
       <c r="D93" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E93" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2269,10 +2275,10 @@
         <v>189</v>
       </c>
       <c r="D94" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E94" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2280,10 +2286,10 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D95" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2297,10 +2303,10 @@
         <v>202</v>
       </c>
       <c r="D96" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E96" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2314,10 +2320,10 @@
         <v>189</v>
       </c>
       <c r="D97" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E97" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2331,10 +2337,10 @@
         <v>202</v>
       </c>
       <c r="D98" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E98" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2348,10 +2354,10 @@
         <v>194</v>
       </c>
       <c r="D99" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E99" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2366,44 +2372,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_D74ED4682C50AE6F9B5226997146C79C2C5CA6F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B2EFA28-22DA-4049-8AD5-C0EAE8DCDCA8}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="234">
   <si>
     <t>targa</t>
   </si>
@@ -335,9 +341,6 @@
     <t>D'ORAZIO CINZIA</t>
   </si>
   <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
     <t>TELEASA GEANINA</t>
   </si>
   <si>
@@ -404,9 +407,6 @@
     <t>CINOSI MELANIA</t>
   </si>
   <si>
-    <t>IN ASSISTENZA - PRONTA AL RITIRO 25-09-26</t>
-  </si>
-  <si>
     <t>FEDERICA.DIREMIGIO</t>
   </si>
   <si>
@@ -491,9 +491,6 @@
     <t>SABINA.LANCIA</t>
   </si>
   <si>
-    <t>CAMISCIA MONIA</t>
-  </si>
-  <si>
     <t>IEZZI.SERENA</t>
   </si>
   <si>
@@ -548,30 +545,33 @@
     <t>CAVUOTO CHIARA</t>
   </si>
   <si>
+    <t>KLODIAN ALIAJ</t>
+  </si>
+  <si>
+    <t>CIMINO NORA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>SECRIERU NATALIE</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE - MINICUCCI</t>
   </si>
   <si>
-    <t>CIMINO NORA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>SECRIERU NATALIE</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
     <t>COTOLLESSA FRANCESCA</t>
   </si>
   <si>
@@ -659,6 +659,9 @@
     <t>2026-08-26</t>
   </si>
   <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
     <t>2026-09-30</t>
   </si>
   <si>
@@ -710,17 +713,26 @@
     <t>Data_Cambio</t>
   </si>
   <si>
-    <t>NORA.CIMINO</t>
+    <t>HC424JD</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - PASQUARELLI</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,22 +761,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -802,7 +823,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -836,6 +857,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -870,9 +892,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1045,11 +1068,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E100"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1074,13 +1101,13 @@
         <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1088,13 +1115,13 @@
         <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1102,1262 +1129,1276 @@
         <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="E5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1">
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E12" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E14" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E19" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E20" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E23" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E25" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E28" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E29" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" t="s">
-        <v>189</v>
+        <v>121</v>
+      </c>
+      <c r="C30" s="2">
+        <v>46311</v>
       </c>
       <c r="E30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E32" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E34" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E35" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E38" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E39" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E40" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E41" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E42" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E44" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E45" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E47" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E50" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E51" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E52" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C53" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E53" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E55" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E57" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E58" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E59" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E60" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E61" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E62" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E63" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E64" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C65" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E65" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E66" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E67" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>232</v>
       </c>
       <c r="C68" s="1">
         <v>46300</v>
       </c>
       <c r="E68" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E69" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E70" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E71" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E72" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E73" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E74" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E75" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E76" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E77" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E78" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E79" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E80" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D82" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E82" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D84" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E84" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D85" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E85" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D86" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E86" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>174</v>
+      </c>
+      <c r="C87" t="s">
+        <v>212</v>
       </c>
       <c r="D87" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D88" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C89" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D89" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E89" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C90" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E90" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C91" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E91" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C92" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D92" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E92" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C93" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D93" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E93" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C94" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D94" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E94" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D95" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C96" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D96" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E96" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C97" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D97" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E97" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C98" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D98" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C99" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D99" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E99" t="s">
-        <v>218</v>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>230</v>
+      </c>
+      <c r="B100" t="s">
+        <v>233</v>
+      </c>
+      <c r="D100" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2366,50 +2407,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" t="s">
         <v>227</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>228</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>229</v>
       </c>
-      <c r="D1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_D74ED4682C50AE6F9B5226997146C79C2C5CA6F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B2EFA28-22DA-4049-8AD5-C0EAE8DCDCA8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="236">
   <si>
     <t>targa</t>
   </si>
@@ -332,6 +326,9 @@
     <t>HC599JE</t>
   </si>
   <si>
+    <t>HC424JD</t>
+  </si>
+  <si>
     <t>IANNONE SAMANTHA</t>
   </si>
   <si>
@@ -341,6 +338,9 @@
     <t>D'ORAZIO CINZIA</t>
   </si>
   <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
     <t>TELEASA GEANINA</t>
   </si>
   <si>
@@ -362,377 +362,377 @@
     <t>DE LUCA ALESSIA</t>
   </si>
   <si>
+    <t>IN ASSISTENZA - PRONTA DA CONSEGNA SI TROVA DA PASQUARELLI</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
+  </si>
+  <si>
+    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
+  </si>
+  <si>
+    <t>VOCIONE MICHELA</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>IN ASSISTENZA  (ERA DEL NOD PESCARA)  06-10-26</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>CAVUOTO CHIARA</t>
+  </si>
+  <si>
+    <t>KLODIAN ALIAJ</t>
+  </si>
+  <si>
+    <t>CIMINO NORA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>SECRIERU NATALIE</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>COTOLLESSA FRANCESCA</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>PARDI ELIANA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - PASQUARELLI</t>
+  </si>
+  <si>
     <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
-  </si>
-  <si>
-    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
-  </si>
-  <si>
-    <t>VOCIONE MICHELA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA  (ERA DEL NOD PESCARA)  06-10-26</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>CAVUOTO CHIARA</t>
-  </si>
-  <si>
-    <t>KLODIAN ALIAJ</t>
-  </si>
-  <si>
-    <t>CIMINO NORA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>SECRIERU NATALIE</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>COTOLLESSA FRANCESCA</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>PARDI ELIANA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-10-09</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-10-16</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>HC424JD</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - PASQUARELLI</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,31 +761,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -823,7 +814,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -857,7 +848,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -892,10 +882,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1068,15 +1057,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1093,1312 +1078,1315 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
+        <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" s="1">
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E23" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E24" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E28" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E29" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="2">
+        <v>123</v>
+      </c>
+      <c r="C30" s="1">
         <v>46311</v>
       </c>
       <c r="E30" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E34" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E42" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E43" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E47" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E50" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E53" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E57" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E58" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E61" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E62" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E63" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E64" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C65" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E65" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E66" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>232</v>
+        <v>158</v>
       </c>
       <c r="C68" s="1">
         <v>46300</v>
       </c>
       <c r="E68" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E71" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E74" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E76" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E77" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E78" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E79" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C80" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E80" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C81" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E81" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D82" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E82" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D83" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E83" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C84" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E85" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C86" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E86" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C87" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D87" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D88" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E89" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D90" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E90" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C91" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E91" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C92" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D92" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E92" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C93" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D93" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E93" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C94" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D94" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E94" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D95" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C96" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D96" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E96" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C97" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D97" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E97" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D98" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E98" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C99" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D99" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E99" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>230</v>
+        <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D100" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2407,36 +2395,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>212</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_010AD31569C3D4B0B5ACF2AC47E7C99C1C55C312" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05E818B4-1DD3-428B-B3F9-221DDEC212A3}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -371,12 +377,6 @@
     <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
   </si>
   <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>IN ASSISTENA- TERMINATA SI PUO ASSEGNARE 09-09-26</t>
-  </si>
-  <si>
     <t>VOCIONE MICHELA</t>
   </si>
   <si>
@@ -434,9 +434,6 @@
     <t>GIADA.GIANSALVO</t>
   </si>
   <si>
-    <t>IN ASSISTENZA  (ERA DEL NOD PESCARA)  06-10-26</t>
-  </si>
-  <si>
     <t>GRAVINA GIUSEPPE</t>
   </si>
   <si>
@@ -723,16 +720,25 @@
   </si>
   <si>
     <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>ROMANO MATTEO</t>
+  </si>
+  <si>
+    <t>DI CRISTOFARO</t>
+  </si>
+  <si>
+    <t>DI TIZIO VALENTINA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,17 +772,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -814,7 +828,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -848,6 +862,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -882,9 +897,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1057,11 +1073,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="62" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1086,13 +1105,13 @@
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1100,13 +1119,13 @@
         <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1114,13 +1133,13 @@
         <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1128,13 +1147,13 @@
         <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1145,10 +1164,10 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1156,13 +1175,13 @@
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1170,10 +1189,10 @@
         <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1181,10 +1200,10 @@
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1192,13 +1211,13 @@
         <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1206,10 +1225,10 @@
         <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1217,13 +1236,13 @@
         <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1231,13 +1250,13 @@
         <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1245,13 +1264,13 @@
         <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1259,1134 +1278,1134 @@
         <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="E16" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="C17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E17" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E20" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E21" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E23" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E24" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E25" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E29" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C30" s="1">
         <v>46311</v>
       </c>
       <c r="E30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E32" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E34" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E35" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E36" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E38" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E39" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E40" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E41" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E42" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E43" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="C44" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E44" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E45" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E46" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E47" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E49" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C50" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E50" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E51" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E52" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E53" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E54" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E55" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E57" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E58" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E59" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E60" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E61" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E62" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E63" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E64" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E65" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E66" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E67" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C68" s="1">
         <v>46300</v>
       </c>
       <c r="E68" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E69" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E70" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E71" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E72" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E73" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E74" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E75" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E76" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E77" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E78" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E79" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E80" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E81" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
+        <v>212</v>
+      </c>
+      <c r="D82" t="s">
         <v>215</v>
       </c>
-      <c r="D82" t="s">
-        <v>218</v>
-      </c>
       <c r="E82" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
+        <v>212</v>
+      </c>
+      <c r="D83" t="s">
         <v>215</v>
       </c>
-      <c r="D83" t="s">
-        <v>218</v>
-      </c>
       <c r="E83" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D84" t="s">
+        <v>216</v>
+      </c>
+      <c r="E84" t="s">
         <v>219</v>
       </c>
-      <c r="E84" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D85" t="s">
+        <v>216</v>
+      </c>
+      <c r="E85" t="s">
         <v>219</v>
       </c>
-      <c r="E85" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D86" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E86" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C87" t="s">
+        <v>213</v>
+      </c>
+      <c r="D87" t="s">
         <v>216</v>
       </c>
-      <c r="D87" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D88" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C89" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D89" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E89" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C90" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D90" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E90" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C91" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E91" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C92" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D92" t="s">
+        <v>216</v>
+      </c>
+      <c r="E92" t="s">
         <v>219</v>
       </c>
-      <c r="E92" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C93" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E93" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C94" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D94" t="s">
+        <v>216</v>
+      </c>
+      <c r="E94" t="s">
         <v>219</v>
       </c>
-      <c r="E94" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D95" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D96" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E96" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C97" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D97" t="s">
+        <v>216</v>
+      </c>
+      <c r="E97" t="s">
         <v>219</v>
       </c>
-      <c r="E97" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D98" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E98" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C99" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D99" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E99" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D100" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -2395,50 +2414,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1" t="s">
         <v>230</v>
       </c>
-      <c r="B1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C2" t="s">
         <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
         <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_010AD31569C3D4B0B5ACF2AC47E7C99C1C55C312" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05E818B4-1DD3-428B-B3F9-221DDEC212A3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="236">
   <si>
     <t>targa</t>
   </si>
@@ -377,6 +371,12 @@
     <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
   </si>
   <si>
+    <t>DI CRISTOFARO</t>
+  </si>
+  <si>
+    <t>DI TIZIO VALENTINA</t>
+  </si>
+  <si>
     <t>VOCIONE MICHELA</t>
   </si>
   <si>
@@ -434,6 +434,9 @@
     <t>GIADA.GIANSALVO</t>
   </si>
   <si>
+    <t>ROMANO MATTEO</t>
+  </si>
+  <si>
     <t>GRAVINA GIUSEPPE</t>
   </si>
   <si>
@@ -488,257 +491,248 @@
     <t>SABINA.LANCIA</t>
   </si>
   <si>
+    <t>DI GIOVANNI FILOMENA  (PRENDERA' LA PANDINA DA MINICUCCI)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>CAVUOTO CHIARA</t>
+  </si>
+  <si>
+    <t>KLODIAN ALIAJ</t>
+  </si>
+  <si>
+    <t>CIMINO NORA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>SECRIERU NATALIE</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - MINICUCCI</t>
+  </si>
+  <si>
+    <t>COTOLLESSA FRANCESCA</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>PARDI ELIANA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>CAVUOTO CHIARA</t>
-  </si>
-  <si>
-    <t>KLODIAN ALIAJ</t>
-  </si>
-  <si>
-    <t>CIMINO NORA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>SECRIERU NATALIE</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>COTOLLESSA FRANCESCA</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>PARDI ELIANA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-10-20</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-10-09</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-10-16</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - PASQUARELLI</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>ROMANO MATTEO</t>
-  </si>
-  <si>
-    <t>DI CRISTOFARO</t>
-  </si>
-  <si>
-    <t>DI TIZIO VALENTINA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,25 +766,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -828,7 +814,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -862,7 +848,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -897,10 +882,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1073,14 +1057,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="62" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1097,7 +1078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1105,13 +1086,13 @@
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1119,13 +1100,13 @@
         <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1133,13 +1114,13 @@
         <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1147,13 +1128,13 @@
         <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1164,10 +1145,10 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1175,13 +1156,13 @@
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1189,10 +1170,10 @@
         <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1200,10 +1181,10 @@
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1211,13 +1192,13 @@
         <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1225,10 +1206,10 @@
         <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1236,13 +1217,13 @@
         <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E12" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1250,13 +1231,13 @@
         <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1264,13 +1245,13 @@
         <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E14" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1278,1134 +1259,1134 @@
         <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>234</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>235</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E23" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E28" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E29" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C30" s="1">
         <v>46311</v>
       </c>
       <c r="E30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E34" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E38" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E42" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E43" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E44" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E45" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E47" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E50" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E53" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E55" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E57" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E58" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E60" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E61" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E62" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E63" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E64" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C65" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E65" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E66" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
-      </c>
-      <c r="C68" s="1">
-        <v>46300</v>
+        <v>158</v>
+      </c>
+      <c r="C68" t="s">
+        <v>211</v>
       </c>
       <c r="E68" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E71" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E74" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E76" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E77" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E78" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E79" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C80" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E80" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C81" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E81" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D82" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E82" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E83" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C84" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D84" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E84" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D85" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E85" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C86" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E86" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C87" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D87" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D88" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D89" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E89" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D90" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E90" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C91" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D91" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E91" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C92" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D92" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E92" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C93" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D93" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E93" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C94" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D94" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E94" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D95" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C96" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D96" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E96" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C97" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D97" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E97" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D98" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C99" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D99" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E99" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D100" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2414,50 +2395,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_77D6330C69F3D72C6EF98EED1247DA9C1C558355" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{219F912C-9E7F-4992-A3C5-730D949F6869}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -728,11 +734,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,17 +772,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -814,7 +828,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -848,6 +862,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -882,9 +897,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1057,11 +1073,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1092,7 +1112,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1106,7 +1126,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1120,7 +1140,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1134,7 +1154,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1148,7 +1168,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1162,7 +1182,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1173,7 +1193,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1184,7 +1204,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1198,7 +1218,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1209,7 +1229,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1223,7 +1243,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1237,7 +1257,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1251,7 +1271,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1265,7 +1285,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1276,7 +1296,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1290,7 +1310,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1304,7 +1324,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1318,7 +1338,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1332,7 +1352,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1346,7 +1366,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1357,7 +1377,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1371,7 +1391,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1385,7 +1405,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1399,7 +1419,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1410,7 +1430,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1421,7 +1441,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1435,7 +1455,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1449,7 +1469,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1463,7 +1483,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1474,7 +1494,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1485,7 +1505,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1499,7 +1519,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1513,7 +1533,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1524,7 +1544,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1535,7 +1555,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1546,7 +1566,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1560,7 +1580,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1571,7 +1591,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1582,7 +1602,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1593,7 +1613,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1607,7 +1627,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1621,7 +1641,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1635,7 +1655,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1649,7 +1669,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1660,7 +1680,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1674,7 +1694,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -1685,7 +1705,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1696,7 +1716,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1710,7 +1730,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -1721,7 +1741,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1732,7 +1752,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -1746,7 +1766,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -1757,7 +1777,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -1771,7 +1791,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -1782,7 +1802,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -1796,7 +1816,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -1807,7 +1827,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -1818,7 +1838,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -1829,7 +1849,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -1840,7 +1860,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -1851,7 +1871,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -1862,7 +1882,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -1876,7 +1896,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1890,7 +1910,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -1901,7 +1921,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -1912,7 +1932,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -1926,7 +1946,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -1937,7 +1957,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1948,7 +1968,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -1962,7 +1982,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -1973,7 +1993,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -1984,7 +2004,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -1998,7 +2018,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -2009,7 +2029,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -2023,7 +2043,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -2034,7 +2054,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -2045,7 +2065,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -2056,7 +2076,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2070,7 +2090,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -2084,7 +2104,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -2101,7 +2121,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -2118,12 +2138,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C84" t="s">
         <v>205</v>
@@ -2135,12 +2155,12 @@
         <v>222</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C85" t="s">
         <v>205</v>
@@ -2152,7 +2172,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -2169,7 +2189,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -2183,7 +2203,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -2197,7 +2217,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2214,7 +2234,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -2231,7 +2251,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -2248,7 +2268,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -2265,7 +2285,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -2282,7 +2302,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -2299,7 +2319,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -2310,7 +2330,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -2327,7 +2347,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -2344,7 +2364,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -2361,7 +2381,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -2378,7 +2398,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>103</v>
       </c>
@@ -2395,11 +2415,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -2413,7 +2433,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -2427,7 +2447,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_77D6330C69F3D72C6EF98EED1247DA9C1C558355" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{219F912C-9E7F-4992-A3C5-730D949F6869}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="236">
   <si>
     <t>targa</t>
   </si>
@@ -545,12 +539,12 @@
     <t>D'ANTONIO VALERIO</t>
   </si>
   <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
     <t>IANNIELLO MILENA</t>
   </si>
   <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
     <t>CAVUOTO CHIARA</t>
   </si>
   <si>
@@ -578,167 +572,167 @@
     <t>BRUNO ANTONIO</t>
   </si>
   <si>
+    <t>ZUCCARINI MARTINA</t>
+  </si>
+  <si>
+    <t>COTOLLESSA FRANCESCA</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>PARDI ELIANA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE - MINICUCCI</t>
-  </si>
-  <si>
-    <t>COTOLLESSA FRANCESCA</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>PARDI ELIANA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-10-20</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-10-09</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-10-21</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-10-16</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - CENTRO DAMA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,25 +766,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -828,7 +814,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -862,7 +848,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -897,10 +882,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1073,15 +1057,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
-    <col min="2" max="2" width="39.42578125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1098,7 +1078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1109,10 +1089,10 @@
         <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1123,10 +1103,10 @@
         <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1137,10 +1117,10 @@
         <v>193</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1151,10 +1131,10 @@
         <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1165,10 +1145,10 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1179,10 +1159,10 @@
         <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1190,10 +1170,10 @@
         <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1201,10 +1181,10 @@
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1215,10 +1195,10 @@
         <v>196</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1226,10 +1206,10 @@
         <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1240,10 +1220,10 @@
         <v>197</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1254,10 +1234,10 @@
         <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1268,10 +1248,10 @@
         <v>198</v>
       </c>
       <c r="E14" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1282,10 +1262,10 @@
         <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1293,10 +1273,10 @@
         <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1307,10 +1287,10 @@
         <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1321,10 +1301,10 @@
         <v>198</v>
       </c>
       <c r="E18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1335,10 +1315,10 @@
         <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1349,10 +1329,10 @@
         <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1363,10 +1343,10 @@
         <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1374,10 +1354,10 @@
         <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1388,10 +1368,10 @@
         <v>191</v>
       </c>
       <c r="E23" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1402,10 +1382,10 @@
         <v>191</v>
       </c>
       <c r="E24" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1416,10 +1396,10 @@
         <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1427,10 +1407,10 @@
         <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1438,10 +1418,10 @@
         <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1452,10 +1432,10 @@
         <v>200</v>
       </c>
       <c r="E28" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1466,10 +1446,10 @@
         <v>203</v>
       </c>
       <c r="E29" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1480,10 +1460,10 @@
         <v>46311</v>
       </c>
       <c r="E30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1491,10 +1471,10 @@
         <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1502,10 +1482,10 @@
         <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1516,10 +1496,10 @@
         <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1530,10 +1510,10 @@
         <v>205</v>
       </c>
       <c r="E34" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1541,10 +1521,10 @@
         <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1552,10 +1532,10 @@
         <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1563,10 +1543,10 @@
         <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1577,10 +1557,10 @@
         <v>206</v>
       </c>
       <c r="E38" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1588,10 +1568,10 @@
         <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1599,10 +1579,10 @@
         <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1610,10 +1590,10 @@
         <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1624,10 +1604,10 @@
         <v>197</v>
       </c>
       <c r="E42" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1638,10 +1618,10 @@
         <v>207</v>
       </c>
       <c r="E43" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1652,10 +1632,10 @@
         <v>192</v>
       </c>
       <c r="E44" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1666,10 +1646,10 @@
         <v>205</v>
       </c>
       <c r="E45" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1677,10 +1657,10 @@
         <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1691,10 +1671,10 @@
         <v>205</v>
       </c>
       <c r="E47" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -1702,10 +1682,10 @@
         <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1713,10 +1693,10 @@
         <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1727,10 +1707,10 @@
         <v>208</v>
       </c>
       <c r="E50" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -1738,10 +1718,10 @@
         <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1749,10 +1729,10 @@
         <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -1763,10 +1743,10 @@
         <v>209</v>
       </c>
       <c r="E53" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -1774,10 +1754,10 @@
         <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -1788,10 +1768,10 @@
         <v>204</v>
       </c>
       <c r="E55" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -1799,10 +1779,10 @@
         <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -1813,10 +1793,10 @@
         <v>207</v>
       </c>
       <c r="E57" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -1824,10 +1804,10 @@
         <v>149</v>
       </c>
       <c r="E58" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -1835,10 +1815,10 @@
         <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -1846,10 +1826,10 @@
         <v>151</v>
       </c>
       <c r="E60" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -1857,10 +1837,10 @@
         <v>152</v>
       </c>
       <c r="E61" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -1868,10 +1848,10 @@
         <v>153</v>
       </c>
       <c r="E62" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -1879,10 +1859,10 @@
         <v>154</v>
       </c>
       <c r="E63" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -1893,10 +1873,10 @@
         <v>210</v>
       </c>
       <c r="E64" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1907,10 +1887,10 @@
         <v>204</v>
       </c>
       <c r="E65" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -1918,10 +1898,10 @@
         <v>156</v>
       </c>
       <c r="E66" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -1929,10 +1909,10 @@
         <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -1943,10 +1923,10 @@
         <v>211</v>
       </c>
       <c r="E68" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -1954,10 +1934,10 @@
         <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1965,10 +1945,10 @@
         <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -1979,10 +1959,10 @@
         <v>211</v>
       </c>
       <c r="E71" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -1990,10 +1970,10 @@
         <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -2001,10 +1981,10 @@
         <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -2015,10 +1995,10 @@
         <v>212</v>
       </c>
       <c r="E74" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -2026,10 +2006,10 @@
         <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -2040,10 +2020,10 @@
         <v>213</v>
       </c>
       <c r="E76" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -2051,10 +2031,10 @@
         <v>167</v>
       </c>
       <c r="E77" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -2062,10 +2042,10 @@
         <v>168</v>
       </c>
       <c r="E78" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -2073,10 +2053,10 @@
         <v>169</v>
       </c>
       <c r="E79" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2087,10 +2067,10 @@
         <v>206</v>
       </c>
       <c r="E80" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -2101,10 +2081,10 @@
         <v>214</v>
       </c>
       <c r="E81" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -2115,13 +2095,13 @@
         <v>215</v>
       </c>
       <c r="D82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E82" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -2132,47 +2112,47 @@
         <v>215</v>
       </c>
       <c r="D83" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E83" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C84" t="s">
         <v>205</v>
       </c>
       <c r="D84" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E84" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s">
         <v>205</v>
       </c>
       <c r="D85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E85" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -2183,13 +2163,13 @@
         <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E86" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -2200,10 +2180,10 @@
         <v>216</v>
       </c>
       <c r="D87" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -2214,10 +2194,10 @@
         <v>208</v>
       </c>
       <c r="D88" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2228,13 +2208,13 @@
         <v>217</v>
       </c>
       <c r="D89" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E89" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -2245,13 +2225,13 @@
         <v>207</v>
       </c>
       <c r="D90" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E90" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -2262,13 +2242,13 @@
         <v>207</v>
       </c>
       <c r="D91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E91" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -2279,13 +2259,13 @@
         <v>191</v>
       </c>
       <c r="D92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E92" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -2296,13 +2276,13 @@
         <v>204</v>
       </c>
       <c r="D93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E93" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -2313,24 +2293,27 @@
         <v>191</v>
       </c>
       <c r="D94" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E94" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
         <v>185</v>
       </c>
+      <c r="C95" t="s">
+        <v>218</v>
+      </c>
       <c r="D95" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -2341,13 +2324,13 @@
         <v>204</v>
       </c>
       <c r="D96" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E96" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -2358,13 +2341,13 @@
         <v>191</v>
       </c>
       <c r="D97" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E97" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -2375,13 +2358,13 @@
         <v>204</v>
       </c>
       <c r="D98" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E98" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -2392,13 +2375,13 @@
         <v>197</v>
       </c>
       <c r="D99" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E99" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>103</v>
       </c>
@@ -2406,7 +2389,7 @@
         <v>190</v>
       </c>
       <c r="D100" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2415,50 +2398,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="237">
   <si>
     <t>targa</t>
   </si>
@@ -380,349 +380,352 @@
     <t>VOCIONE MICHELA</t>
   </si>
   <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>SELLINI CRISTAL</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>MELIDEI GRETA</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t>LEPORATI MELANY</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>ROMANO MATTEO</t>
+  </si>
+  <si>
+    <t>GRAVINA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DI GIOVANNI FILOMENA  (PRENDERA' LA PANDINA DA MINICUCCI)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>PATELLA ERIKA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>CAMPLONE STEFANO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>TREPSENISHTI MIMOZA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV</t>
+  </si>
+  <si>
+    <t>BIANCO DANIELA</t>
+  </si>
+  <si>
+    <t>DESPAIGNE  YOEL</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO</t>
+  </si>
+  <si>
+    <t>FALCONIO FELICIA</t>
+  </si>
+  <si>
+    <t>IANNIELLO MILENA</t>
+  </si>
+  <si>
+    <t>CAVUOTO CHIARA</t>
+  </si>
+  <si>
+    <t>KLODIAN ALIAJ</t>
+  </si>
+  <si>
+    <t>CIMINO NORA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO</t>
+  </si>
+  <si>
+    <t>TURDO' SIMONA</t>
+  </si>
+  <si>
+    <t>D'ORTONA LORELLA</t>
+  </si>
+  <si>
+    <t>LUCIANO MARIA</t>
+  </si>
+  <si>
+    <t>SECRIERU NATALIE</t>
+  </si>
+  <si>
+    <t>BRUNO ANTONIO</t>
+  </si>
+  <si>
+    <t>ZUCCARINI MARTINA</t>
+  </si>
+  <si>
+    <t>COTOLLESSA FRANCESCA</t>
+  </si>
+  <si>
+    <t>LUCIANO JANE</t>
+  </si>
+  <si>
+    <t>PARDI ELIANA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-10-26</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
+  </si>
+  <si>
+    <t>berlingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandina </t>
+  </si>
+  <si>
+    <t>CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>VASTO</t>
+  </si>
+  <si>
+    <t>SANGRO AVENTINO</t>
+  </si>
+  <si>
+    <t>ORTONA</t>
+  </si>
+  <si>
+    <t>CHIETI</t>
+  </si>
+  <si>
+    <t>PASQUARELLI</t>
+  </si>
+  <si>
+    <t>LANCIANO</t>
+  </si>
+  <si>
+    <t>FRANCAVILLA AL MARE</t>
+  </si>
+  <si>
+    <t>PESCARA</t>
+  </si>
+  <si>
+    <t>VASTO COSTA SUD</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
   </si>
   <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>SELLINI CRISTAL</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>MELIDEI GRETA</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t>LEPORATI MELANY</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>ROMANO MATTEO</t>
-  </si>
-  <si>
-    <t>GRAVINA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DI GIOVANNI FILOMENA  (PRENDERA' LA PANDINA DA MINICUCCI)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
     <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>CAMPLONE STEFANO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>TREPSENISHTI MIMOZA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV</t>
-  </si>
-  <si>
-    <t>BIANCO DANIELA</t>
-  </si>
-  <si>
-    <t>DESPAIGNE  YOEL</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO</t>
-  </si>
-  <si>
-    <t>FALCONIO FELICIA</t>
-  </si>
-  <si>
-    <t>IANNIELLO MILENA</t>
-  </si>
-  <si>
-    <t>CAVUOTO CHIARA</t>
-  </si>
-  <si>
-    <t>KLODIAN ALIAJ</t>
-  </si>
-  <si>
-    <t>CIMINO NORA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO</t>
-  </si>
-  <si>
-    <t>TURDO' SIMONA</t>
-  </si>
-  <si>
-    <t>D'ORTONA LORELLA</t>
-  </si>
-  <si>
-    <t>LUCIANO MARIA</t>
-  </si>
-  <si>
-    <t>SECRIERU NATALIE</t>
-  </si>
-  <si>
-    <t>BRUNO ANTONIO</t>
-  </si>
-  <si>
-    <t>ZUCCARINI MARTINA</t>
-  </si>
-  <si>
-    <t>COTOLLESSA FRANCESCA</t>
-  </si>
-  <si>
-    <t>LUCIANO JANE</t>
-  </si>
-  <si>
-    <t>PARDI ELIANA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - CENTRO DAMA - CANDELORO ?</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-10-20</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-10-09</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-10-21</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-10-16</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>2026-10-23</t>
-  </si>
-  <si>
-    <t>berlingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pandina </t>
-  </si>
-  <si>
-    <t>CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>VASTO</t>
-  </si>
-  <si>
-    <t>SANGRO AVENTINO</t>
-  </si>
-  <si>
-    <t>ORTONA</t>
-  </si>
-  <si>
-    <t>CHIETI</t>
-  </si>
-  <si>
-    <t>PASQUARELLI</t>
-  </si>
-  <si>
-    <t>LANCIANO</t>
-  </si>
-  <si>
-    <t>FRANCAVILLA AL MARE</t>
-  </si>
-  <si>
-    <t>PESCARA</t>
-  </si>
-  <si>
-    <t>VASTO COSTA SUD</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE - MINICUCCI</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1089,7 @@
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
         <v>221</v>
@@ -1100,7 +1103,7 @@
         <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E3" t="s">
         <v>222</v>
@@ -1114,7 +1117,7 @@
         <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E4" t="s">
         <v>223</v>
@@ -1128,7 +1131,7 @@
         <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E5" t="s">
         <v>223</v>
@@ -1156,7 +1159,7 @@
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E7" t="s">
         <v>221</v>
@@ -1192,7 +1195,7 @@
         <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E10" t="s">
         <v>223</v>
@@ -1217,7 +1220,7 @@
         <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E12" t="s">
         <v>224</v>
@@ -1231,7 +1234,7 @@
         <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E13" t="s">
         <v>221</v>
@@ -1245,7 +1248,7 @@
         <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E14" t="s">
         <v>226</v>
@@ -1259,7 +1262,7 @@
         <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E15" t="s">
         <v>225</v>
@@ -1284,7 +1287,7 @@
         <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E17" t="s">
         <v>225</v>
@@ -1298,7 +1301,7 @@
         <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E18" t="s">
         <v>225</v>
@@ -1309,10 +1312,10 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E19" t="s">
         <v>226</v>
@@ -1323,10 +1326,10 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E20" t="s">
         <v>227</v>
@@ -1337,10 +1340,10 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
         <v>223</v>
@@ -1351,7 +1354,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
         <v>228</v>
@@ -1362,10 +1365,10 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E23" t="s">
         <v>223</v>
@@ -1376,10 +1379,10 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E24" t="s">
         <v>223</v>
@@ -1390,10 +1393,10 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E25" t="s">
         <v>225</v>
@@ -1404,7 +1407,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
         <v>229</v>
@@ -1415,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
         <v>228</v>
@@ -1426,10 +1429,10 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
         <v>228</v>
@@ -1440,7 +1443,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
         <v>203</v>
@@ -1454,7 +1457,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" s="1">
         <v>46311</v>
@@ -1468,7 +1471,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s">
         <v>224</v>
@@ -1479,7 +1482,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E32" t="s">
         <v>228</v>
@@ -1490,7 +1493,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
         <v>204</v>
@@ -1504,7 +1507,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
         <v>205</v>
@@ -1518,7 +1521,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s">
         <v>227</v>
@@ -1529,7 +1532,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
         <v>228</v>
@@ -1540,7 +1543,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
         <v>222</v>
@@ -1551,7 +1554,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
         <v>206</v>
@@ -1565,7 +1568,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
         <v>228</v>
@@ -1576,7 +1579,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
         <v>225</v>
@@ -1587,7 +1590,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E41" t="s">
         <v>228</v>
@@ -1598,10 +1601,10 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E42" t="s">
         <v>224</v>
@@ -1612,7 +1615,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
         <v>207</v>
@@ -1626,10 +1629,10 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E44" t="s">
         <v>229</v>
@@ -1640,7 +1643,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
         <v>205</v>
@@ -1654,7 +1657,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
         <v>228</v>
@@ -1665,7 +1668,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" t="s">
         <v>205</v>
@@ -1679,7 +1682,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
         <v>225</v>
@@ -1690,7 +1693,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E49" t="s">
         <v>223</v>
@@ -1701,7 +1704,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C50" t="s">
         <v>208</v>
@@ -1715,7 +1718,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E51" t="s">
         <v>225</v>
@@ -1726,7 +1729,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E52" t="s">
         <v>223</v>
@@ -1737,7 +1740,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C53" t="s">
         <v>209</v>
@@ -1751,7 +1754,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
         <v>229</v>
@@ -1762,7 +1765,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C55" t="s">
         <v>204</v>
@@ -1776,7 +1779,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E56" t="s">
         <v>227</v>
@@ -1787,7 +1790,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C57" t="s">
         <v>207</v>
@@ -1801,7 +1804,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
         <v>228</v>
@@ -1812,7 +1815,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E59" t="s">
         <v>225</v>
@@ -1823,7 +1826,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E60" t="s">
         <v>222</v>
@@ -1834,7 +1837,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E61" t="s">
         <v>225</v>
@@ -1845,7 +1848,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E62" t="s">
         <v>223</v>
@@ -1856,7 +1859,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E63" t="s">
         <v>225</v>
@@ -1867,7 +1870,7 @@
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C64" t="s">
         <v>210</v>
@@ -1881,7 +1884,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C65" t="s">
         <v>204</v>
@@ -1895,7 +1898,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E66" t="s">
         <v>222</v>
@@ -1906,7 +1909,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E67" t="s">
         <v>227</v>
@@ -1917,7 +1920,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
         <v>211</v>
@@ -1931,7 +1934,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E69" t="s">
         <v>228</v>
@@ -1942,7 +1945,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E70" t="s">
         <v>223</v>
@@ -1953,10 +1956,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C71" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E71" t="s">
         <v>225</v>
@@ -1967,7 +1970,10 @@
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>161</v>
+      </c>
+      <c r="C72" t="s">
+        <v>199</v>
       </c>
       <c r="E72" t="s">
         <v>225</v>
@@ -1978,7 +1984,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E73" t="s">
         <v>227</v>
@@ -1989,7 +1995,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C74" t="s">
         <v>212</v>
@@ -2003,7 +2009,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E75" t="s">
         <v>228</v>
@@ -2014,7 +2020,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C76" t="s">
         <v>213</v>
@@ -2028,7 +2034,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E77" t="s">
         <v>223</v>
@@ -2039,7 +2045,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E78" t="s">
         <v>223</v>
@@ -2050,7 +2056,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E79" t="s">
         <v>223</v>
@@ -2061,7 +2067,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C80" t="s">
         <v>206</v>
@@ -2075,7 +2081,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C81" t="s">
         <v>214</v>
@@ -2089,7 +2095,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C82" t="s">
         <v>215</v>
@@ -2106,7 +2112,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
         <v>215</v>
@@ -2123,7 +2129,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C84" t="s">
         <v>205</v>
@@ -2140,7 +2146,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C85" t="s">
         <v>205</v>
@@ -2157,10 +2163,10 @@
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C86" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D86" t="s">
         <v>220</v>
@@ -2174,7 +2180,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C87" t="s">
         <v>216</v>
@@ -2188,7 +2194,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C88" t="s">
         <v>208</v>
@@ -2202,7 +2208,7 @@
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C89" t="s">
         <v>217</v>
@@ -2219,7 +2225,7 @@
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C90" t="s">
         <v>207</v>
@@ -2236,7 +2242,7 @@
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C91" t="s">
         <v>207</v>
@@ -2253,10 +2259,10 @@
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C92" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D92" t="s">
         <v>220</v>
@@ -2270,7 +2276,7 @@
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C93" t="s">
         <v>204</v>
@@ -2287,10 +2293,10 @@
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D94" t="s">
         <v>220</v>
@@ -2304,7 +2310,7 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C95" t="s">
         <v>218</v>
@@ -2318,7 +2324,7 @@
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C96" t="s">
         <v>204</v>
@@ -2335,10 +2341,10 @@
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C97" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D97" t="s">
         <v>220</v>
@@ -2352,7 +2358,7 @@
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C98" t="s">
         <v>204</v>
@@ -2369,10 +2375,10 @@
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C99" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D99" t="s">
         <v>220</v>
@@ -2386,7 +2392,7 @@
         <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D100" t="s">
         <v>220</v>
@@ -2399,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2418,16 +2424,44 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
         <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>218</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="236">
   <si>
     <t>targa</t>
   </si>
@@ -338,48 +338,51 @@
     <t>D'ORAZIO CINZIA</t>
   </si>
   <si>
+    <t>IN ASSISTENZA</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>DE LUCA ALESSIA</t>
+  </si>
+  <si>
     <t>MASCIARELLI MAURIZIO</t>
   </si>
   <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>DE LUCA ALESSIA</t>
+    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
+  </si>
+  <si>
+    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
+  </si>
+  <si>
+    <t>DI CRISTOFARO</t>
+  </si>
+  <si>
+    <t>DI TIZIO VALENTINA</t>
+  </si>
+  <si>
+    <t>VOCIONE MICHELA</t>
   </si>
   <si>
     <t>IN ASSISTENZA - PRONTA DA CONSEGNA SI TROVA DA PASQUARELLI</t>
   </si>
   <si>
-    <t>IN ASSISTENZA - REVISIONE + MANUTENZIONE</t>
-  </si>
-  <si>
-    <t>MONACO BENEDETTA - ASS. TEMPORANEA NO DKV</t>
-  </si>
-  <si>
-    <t>DI CRISTOFARO</t>
-  </si>
-  <si>
-    <t>DI TIZIO VALENTINA</t>
-  </si>
-  <si>
-    <t>VOCIONE MICHELA</t>
-  </si>
-  <si>
     <t>BONFITTO DAVIDE</t>
   </si>
   <si>
@@ -596,7 +599,7 @@
     <t>2026-08-18</t>
   </si>
   <si>
-    <t>2026-10-20</t>
+    <t>2026-10-30</t>
   </si>
   <si>
     <t>2026-05-07</t>
@@ -720,12 +723,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>IN ASSISTENZA ( POI DA ASSEGNARE)</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
   </si>
 </sst>
 </file>
@@ -1089,10 +1086,10 @@
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1103,10 +1100,10 @@
         <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1117,10 +1114,10 @@
         <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1131,10 +1128,10 @@
         <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1148,7 +1145,7 @@
         <v>45851</v>
       </c>
       <c r="E6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1159,10 +1156,10 @@
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1173,7 +1170,7 @@
         <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1184,7 +1181,7 @@
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1195,10 +1192,10 @@
         <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1209,7 +1206,7 @@
         <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1220,10 +1217,10 @@
         <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1234,10 +1231,10 @@
         <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1248,10 +1245,10 @@
         <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1262,10 +1259,10 @@
         <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1276,7 +1273,7 @@
         <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1287,10 +1284,10 @@
         <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1301,10 +1298,10 @@
         <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1312,13 +1309,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1326,13 +1323,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1340,13 +1337,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1354,10 +1351,10 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1365,13 +1362,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1379,13 +1376,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1393,13 +1390,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1407,10 +1404,10 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1418,10 +1415,10 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1429,13 +1426,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1443,13 +1440,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1457,13 +1454,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="1">
         <v>46311</v>
       </c>
       <c r="E30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1471,10 +1468,10 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1482,10 +1479,10 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1493,13 +1490,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E33" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1507,13 +1504,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1521,10 +1518,10 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1532,10 +1529,10 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1543,10 +1540,10 @@
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1554,13 +1551,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E38" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1568,10 +1565,10 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1579,10 +1576,10 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1590,10 +1587,10 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E41" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1601,13 +1598,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E42" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1615,13 +1612,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1629,13 +1626,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E44" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1643,13 +1640,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E45" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1657,10 +1654,10 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1668,13 +1665,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E47" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1682,10 +1679,10 @@
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1693,10 +1690,10 @@
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1704,13 +1701,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1718,10 +1715,10 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1729,10 +1726,10 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1740,13 +1737,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1754,10 +1751,10 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1765,13 +1762,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E55" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1779,10 +1776,10 @@
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1790,13 +1787,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1804,10 +1801,10 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E58" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1815,10 +1812,10 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1826,10 +1823,10 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E60" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1837,10 +1834,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E61" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1848,10 +1845,10 @@
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E62" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1859,10 +1856,10 @@
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E63" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1870,13 +1867,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E64" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1884,13 +1881,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1898,10 +1895,10 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E66" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1909,10 +1906,10 @@
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1920,13 +1917,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E68" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1934,10 +1931,10 @@
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1945,10 +1942,10 @@
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1956,13 +1953,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E71" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1970,13 +1967,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E72" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1984,10 +1981,10 @@
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1995,13 +1992,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C74" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E74" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2009,10 +2006,10 @@
         <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2020,13 +2017,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2034,10 +2031,10 @@
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2045,10 +2042,10 @@
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E78" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2056,10 +2053,10 @@
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2067,13 +2064,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C80" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2081,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C81" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E81" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2095,16 +2092,16 @@
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D82" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2112,16 +2109,16 @@
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D83" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2129,16 +2126,16 @@
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C84" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D84" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E84" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2146,16 +2143,16 @@
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D85" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2163,16 +2160,16 @@
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E86" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2180,13 +2177,13 @@
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C87" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D87" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2194,13 +2191,13 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D88" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2208,16 +2205,16 @@
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D89" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E89" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2225,16 +2222,16 @@
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D90" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E90" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2242,16 +2239,16 @@
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D91" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E91" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2259,16 +2256,16 @@
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C92" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2276,16 +2273,16 @@
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C93" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D93" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E93" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2293,16 +2290,16 @@
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C94" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E94" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2310,13 +2307,13 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C95" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D95" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2324,16 +2321,16 @@
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D96" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E96" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2341,16 +2338,16 @@
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C97" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D97" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E97" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2358,16 +2355,16 @@
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D98" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E98" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2375,16 +2372,16 @@
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C99" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D99" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E99" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2392,10 +2389,10 @@
         <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D100" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2405,63 +2402,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_3BAE72136963DC2B3E3B82587264C79C1C55D335" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1C80C71-58AC-4207-AE5B-F8C5D5873276}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="236">
   <si>
     <t>targa</t>
   </si>
@@ -728,11 +734,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,22 +767,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -814,7 +829,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -848,6 +863,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -882,9 +898,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1057,11 +1074,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1092,7 +1112,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1106,7 +1126,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1120,7 +1140,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1134,7 +1154,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1148,7 +1168,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1162,7 +1182,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1173,7 +1193,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1184,7 +1204,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1198,7 +1218,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1209,7 +1229,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1223,7 +1243,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1237,7 +1257,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1251,7 +1271,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1265,7 +1285,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1276,7 +1296,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1290,7 +1310,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1304,21 +1324,21 @@
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" t="s">
-        <v>200</v>
+        <v>162</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46321</v>
       </c>
       <c r="E19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1332,7 +1352,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1346,7 +1366,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1357,7 +1377,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1371,7 +1391,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1385,7 +1405,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1399,7 +1419,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1410,7 +1430,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1421,7 +1441,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1435,7 +1455,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1449,7 +1469,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1463,7 +1483,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1474,7 +1494,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1485,7 +1505,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1499,7 +1519,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1513,7 +1533,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1524,7 +1544,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1535,7 +1555,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1546,7 +1566,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1560,7 +1580,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1571,7 +1591,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1582,7 +1602,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1593,7 +1613,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1607,7 +1627,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1621,7 +1641,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1635,7 +1655,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1649,7 +1669,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1660,7 +1680,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1674,7 +1694,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -1685,7 +1705,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1696,7 +1716,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1710,7 +1730,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -1721,7 +1741,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1732,7 +1752,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -1746,7 +1766,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -1757,7 +1777,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -1771,7 +1791,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -1782,7 +1802,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -1796,7 +1816,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -1807,7 +1827,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -1818,7 +1838,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -1829,7 +1849,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -1840,7 +1860,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -1851,7 +1871,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -1862,7 +1882,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -1876,7 +1896,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1890,7 +1910,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -1901,7 +1921,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -1912,7 +1932,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -1926,7 +1946,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -1937,7 +1957,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1948,7 +1968,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -1962,7 +1982,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -1976,7 +1996,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -1987,7 +2007,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -2001,7 +2021,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -2012,7 +2032,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -2026,7 +2046,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -2037,7 +2057,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -2048,7 +2068,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -2059,7 +2079,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2073,7 +2093,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -2087,7 +2107,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -2104,7 +2124,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -2121,7 +2141,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -2138,7 +2158,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -2155,7 +2175,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -2172,7 +2192,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -2186,7 +2206,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -2200,7 +2220,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2217,7 +2237,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -2234,7 +2254,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -2251,7 +2271,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -2268,7 +2288,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -2285,7 +2305,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -2302,7 +2322,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -2316,7 +2336,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -2333,7 +2353,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -2350,7 +2370,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -2367,7 +2387,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -2384,7 +2404,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>103</v>
       </c>
@@ -2401,11 +2421,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>232</v>
       </c>
@@ -2419,7 +2439,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2433,7 +2453,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
